--- a/franquias/pwr_reports/Keys Summary - Franquias (Stores)(2026-08-03 - 2026-08-09).xlsx
+++ b/franquias/pwr_reports/Keys Summary - Franquias (Stores)(2026-08-03 - 2026-08-09).xlsx
@@ -888,63 +888,63 @@
 165</t>
   </si>
   <si>
-    <t>155</t>
-  </si>
-  <si>
-    <t>R$ 6.916.907,07</t>
-  </si>
-  <si>
-    <t>R$ 41.956,98
-R$ 40.593,24</t>
-  </si>
-  <si>
-    <t>9.2%
-8.4%</t>
-  </si>
-  <si>
-    <t>452.8</t>
-  </si>
-  <si>
-    <t>(4.2%)</t>
-  </si>
-  <si>
-    <t>16.4%</t>
-  </si>
-  <si>
-    <t>(26.3%)</t>
-  </si>
-  <si>
-    <t>3.1%</t>
-  </si>
-  <si>
-    <t>0.5%</t>
-  </si>
-  <si>
-    <t>28.0</t>
-  </si>
-  <si>
-    <t>64.6%</t>
-  </si>
-  <si>
-    <t>11.9%</t>
+    <t>121</t>
+  </si>
+  <si>
+    <t>R$ 7.184.767,98</t>
+  </si>
+  <si>
+    <t>R$ 42.334,49
+R$ 42.104,13</t>
+  </si>
+  <si>
+    <t>10.2%
+9.8%</t>
+  </si>
+  <si>
+    <t>457.0</t>
+  </si>
+  <si>
+    <t>(4.4%)</t>
+  </si>
+  <si>
+    <t>17.0%</t>
+  </si>
+  <si>
+    <t>(25.7%)</t>
+  </si>
+  <si>
+    <t>3.2%</t>
+  </si>
+  <si>
+    <t>0.6%</t>
+  </si>
+  <si>
+    <t>28.1</t>
+  </si>
+  <si>
+    <t>64.5%</t>
+  </si>
+  <si>
+    <t>12.1%</t>
   </si>
   <si>
     <t>5.7</t>
   </si>
   <si>
-    <t>7.2</t>
+    <t>7.3</t>
   </si>
   <si>
     <t>13.0</t>
   </si>
   <si>
-    <t>19.6</t>
-  </si>
-  <si>
-    <t>68.2%</t>
-  </si>
-  <si>
-    <t>-R$ 186.817,96</t>
+    <t>19.7</t>
+  </si>
+  <si>
+    <t>67.9%</t>
+  </si>
+  <si>
+    <t>-R$ 192.001,94</t>
   </si>
   <si>
     <t>2.72</t>
@@ -2079,7 +2079,7 @@
         <v>19521</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>44</v>
@@ -2119,22 +2119,22 @@
         <v>73769.509999999995</v>
       </c>
       <c r="P6" s="5">
-        <v>86064.42833333333</v>
+        <v>73769.509999999995</v>
       </c>
       <c r="Q6" s="6">
-        <v>0.40558675382402232</v>
+        <v>0.20478864613487624</v>
       </c>
       <c r="R6" s="7">
-        <v>866.83333333333326</v>
+        <v>743</v>
       </c>
       <c r="S6" s="6">
-        <v>0.058404558404558271</v>
+        <v>0.058404558404558493</v>
       </c>
       <c r="T6" s="6">
-        <v>0.00096191502424240044</v>
+        <v>-0.0010728009444552363</v>
       </c>
       <c r="U6" s="6">
-        <v>-0.33708370843184404</v>
+        <v>-0.33911842440054163</v>
       </c>
       <c r="V6" s="6">
         <v>0.040623585543675164</v>
@@ -3353,7 +3353,7 @@
         <v>19546</v>
       </c>
       <c r="B16" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C16" s="4">
         <v>44</v>
@@ -3390,59 +3390,59 @@
         <v>52</v>
       </c>
       <c r="O16" s="5">
-        <v>37063.93</v>
+        <v>45140.139999999999</v>
       </c>
       <c r="P16" s="5">
-        <v>43241.251666666671</v>
+        <v>45140.139999999999</v>
       </c>
       <c r="Q16" s="6">
-        <v>0.12504882702398001</v>
+        <v>0.17445401326915588</v>
       </c>
       <c r="R16" s="7">
-        <v>473.66666666666669</v>
+        <v>493</v>
       </c>
       <c r="S16" s="6">
-        <v>-0.031026252983293534</v>
+        <v>-0.021825396825396859</v>
       </c>
       <c r="T16" s="6">
-        <v>-0.00020842366149515174</v>
+        <v>-0.00011479583359732601</v>
       </c>
       <c r="U16" s="6">
-        <v>-0.31066470824869352</v>
+        <v>-0.31161028521400247</v>
       </c>
       <c r="V16" s="6">
-        <v>0.053572206185366747</v>
+        <v>0.055576289750098255</v>
       </c>
       <c r="W16" s="6">
-        <v>0.044445812950758321</v>
+        <v>0.046846587095210605</v>
       </c>
       <c r="X16" s="8">
-        <v>27.998265158371041</v>
+        <v>28.331077443609022</v>
       </c>
       <c r="Y16" s="6">
-        <v>0.61711711711711714</v>
+        <v>0.60299625468164797</v>
       </c>
       <c r="Z16" s="6">
-        <v>0.11764705882352941</v>
+        <v>0.10902255639097744</v>
       </c>
       <c r="AA16" s="8">
-        <v>3.8390573232323231</v>
+        <v>3.9391078838174276</v>
       </c>
       <c r="AB16" s="8">
-        <v>8.2676557077625574</v>
+        <v>8.2512624999999993</v>
       </c>
       <c r="AC16" s="8">
-        <v>12.084775</v>
+        <v>12.146813</v>
       </c>
       <c r="AD16" s="8">
-        <v>18.929109954751134</v>
+        <v>19.007268045112781</v>
       </c>
       <c r="AE16" s="6">
-        <v>0.65610859728506787</v>
+        <v>0.6278195488721805</v>
       </c>
       <c r="AF16" s="9"/>
       <c r="AG16" s="5">
-        <v>-6337.6999999999998</v>
+        <v>-7384.9200000000001</v>
       </c>
       <c r="AH16" s="10">
         <v>2</v>
@@ -3615,7 +3615,7 @@
         <v>19550</v>
       </c>
       <c r="B18" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C18" s="4">
         <v>44</v>
@@ -3652,51 +3652,51 @@
         <v>52</v>
       </c>
       <c r="O18" s="5">
-        <v>30917.299999999999</v>
+        <v>38828.729999999996</v>
       </c>
       <c r="P18" s="5">
-        <v>36070.183333333334</v>
+        <v>38828.729999999996</v>
       </c>
       <c r="Q18" s="6"/>
       <c r="R18" s="7">
-        <v>338.33333333333337</v>
+        <v>367</v>
       </c>
       <c r="S18" s="6"/>
       <c r="T18" s="6">
-        <v>0.40683267296950248</v>
+        <v>0.4027910570343145</v>
       </c>
       <c r="U18" s="6">
-        <v>-0.052417649665397692</v>
+        <v>-0.049627809099087192</v>
       </c>
       <c r="V18" s="6">
-        <v>0.034820893156905681</v>
+        <v>0.031293619441068503</v>
       </c>
       <c r="W18" s="6">
-        <v>0.0016883104281421729</v>
+        <v>0.00040824152631311911</v>
       </c>
       <c r="X18" s="8">
-        <v>18.829914529914529</v>
+        <v>19.913541666666667</v>
       </c>
       <c r="Y18" s="6">
-        <v>0.9145299145299145</v>
+        <v>0.875</v>
       </c>
       <c r="Z18" s="6">
-        <v>0</v>
+        <v>0.034722222222222224</v>
       </c>
       <c r="AA18" s="8">
-        <v>2.0526733788395903</v>
+        <v>2.1960359459459462</v>
       </c>
       <c r="AB18" s="8">
-        <v>1.8622504273504272</v>
+        <v>2.6280090277777775</v>
       </c>
       <c r="AC18" s="8">
-        <v>3.8420809999999999</v>
+        <v>4.6880540000000002</v>
       </c>
       <c r="AD18" s="8">
-        <v>10.819088888888889</v>
+        <v>11.664236805555555</v>
       </c>
       <c r="AE18" s="6">
-        <v>0.99145299145299148</v>
+        <v>0.95833333333333337</v>
       </c>
       <c r="AF18" s="9"/>
       <c r="AG18" s="5">
@@ -4006,7 +4006,7 @@
         <v>19553</v>
       </c>
       <c r="B21" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C21" s="4">
         <v>44</v>
@@ -4041,55 +4041,55 @@
         <v>52</v>
       </c>
       <c r="O21" s="5">
-        <v>45258.550000000003</v>
+        <v>59362</v>
       </c>
       <c r="P21" s="5">
-        <v>52801.64166666667</v>
+        <v>59362</v>
       </c>
       <c r="Q21" s="6">
-        <v>0.22471816508285536</v>
+        <v>0.3768836994616509</v>
       </c>
       <c r="R21" s="7">
-        <v>484.16666666666669</v>
+        <v>544</v>
       </c>
       <c r="S21" s="6">
-        <v>0.11260053619302957</v>
+        <v>0.11704312114989723</v>
       </c>
       <c r="T21" s="6">
-        <v>0.29737808215243305</v>
+        <v>0.3166532815605943</v>
       </c>
       <c r="U21" s="6">
-        <v>-0.051932048198627664</v>
+        <v>-0.028098748357535126</v>
       </c>
       <c r="V21" s="6">
-        <v>0.026578867418421491</v>
+        <v>0.025177091405276103</v>
       </c>
       <c r="W21" s="6">
-        <v>-0.00077508006774410572</v>
+        <v>0.00051535494087126446</v>
       </c>
       <c r="X21" s="8">
-        <v>25.24530612244898</v>
+        <v>25.329475308641975</v>
       </c>
       <c r="Y21" s="6">
-        <v>0.85306122448979593</v>
+        <v>0.83950617283950613</v>
       </c>
       <c r="Z21" s="6">
-        <v>0.040816326530612242</v>
+        <v>0.033950617283950615</v>
       </c>
       <c r="AA21" s="8">
-        <v>3.1500395238095238</v>
+        <v>3.3617270909090911</v>
       </c>
       <c r="AB21" s="8">
-        <v>6.5609049382716051</v>
+        <v>6.6585146417445493</v>
       </c>
       <c r="AC21" s="8">
-        <v>9.8548069999999992</v>
+        <v>10.086411999999999</v>
       </c>
       <c r="AD21" s="8">
-        <v>16.72476244897959</v>
+        <v>16.952109567901235</v>
       </c>
       <c r="AE21" s="6">
-        <v>0.82040816326530608</v>
+        <v>0.80864197530864201</v>
       </c>
       <c r="AF21" s="9"/>
       <c r="AG21" s="5">
@@ -4397,7 +4397,7 @@
         <v>19565</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>44</v>
@@ -4434,59 +4434,59 @@
         <v>52</v>
       </c>
       <c r="O24" s="5">
-        <v>36883.779999999999</v>
+        <v>53742.440000000002</v>
       </c>
       <c r="P24" s="5">
-        <v>43031.076666666668</v>
+        <v>53742.440000000002</v>
       </c>
       <c r="Q24" s="6">
-        <v>-0.11222333148547825</v>
+        <v>0.10876343417175893</v>
       </c>
       <c r="R24" s="7">
-        <v>480.66666666666669</v>
+        <v>591</v>
       </c>
       <c r="S24" s="6">
-        <v>-0.1177730192719485</v>
+        <v>-0.070754716981132115</v>
       </c>
       <c r="T24" s="6">
-        <v>0.28048381700574077</v>
+        <v>0.26992914166159926</v>
       </c>
       <c r="U24" s="6">
-        <v>-0.036474748520894551</v>
+        <v>-0.043949238255650468</v>
       </c>
       <c r="V24" s="6">
-        <v>0.088868331824991917</v>
+        <v>0.081463011355643683</v>
       </c>
       <c r="W24" s="6">
-        <v>0.049689592552607138</v>
+        <v>0.048840004287114609</v>
       </c>
       <c r="X24" s="8">
-        <v>24.035211267605632</v>
+        <v>25.871267070217918</v>
       </c>
       <c r="Y24" s="6">
-        <v>0.99295774647887325</v>
+        <v>0.9371980676328503</v>
       </c>
       <c r="Z24" s="6">
-        <v>0.045774647887323945</v>
+        <v>0.067796610169491525</v>
       </c>
       <c r="AA24" s="8">
-        <v>3.1002412048192776</v>
+        <v>3.3049581512605042</v>
       </c>
       <c r="AB24" s="8">
-        <v>6.2859212121212114</v>
+        <v>7.4891579081632651</v>
       </c>
       <c r="AC24" s="8">
-        <v>9.3004309999999997</v>
+        <v>10.723295999999999</v>
       </c>
       <c r="AD24" s="8">
-        <v>16.465551760563379</v>
+        <v>18.035351089588378</v>
       </c>
       <c r="AE24" s="6">
-        <v>0.80633802816901412</v>
+        <v>0.73123486682808714</v>
       </c>
       <c r="AF24" s="9"/>
       <c r="AG24" s="5">
-        <v>0</v>
+        <v>105.75</v>
       </c>
       <c r="AH24" s="10">
         <v>4</v>
@@ -5314,7 +5314,7 @@
         <v>19596</v>
       </c>
       <c r="B31" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C31" s="4">
         <v>44</v>
@@ -5349,59 +5349,59 @@
         <v>52</v>
       </c>
       <c r="O31" s="5">
-        <v>38049.909999999996</v>
+        <v>48944.869999999995</v>
       </c>
       <c r="P31" s="5">
-        <v>44391.561666666668</v>
+        <v>48944.869999999995</v>
       </c>
       <c r="Q31" s="6">
-        <v>0.15273954057886474</v>
+        <v>0.27097774530104402</v>
       </c>
       <c r="R31" s="7">
-        <v>499.33333333333331</v>
+        <v>537</v>
       </c>
       <c r="S31" s="6">
-        <v>0.07268170426065157</v>
+        <v>0.11642411642411665</v>
       </c>
       <c r="T31" s="6">
-        <v>0.38471788500945203</v>
+        <v>0.37814237733188377</v>
       </c>
       <c r="U31" s="6">
-        <v>0.0087798078891645204</v>
+        <v>-0.0041524372217149616</v>
       </c>
       <c r="V31" s="6">
-        <v>0.053094448843637211</v>
+        <v>0.071799179362413257</v>
       </c>
       <c r="W31" s="6">
-        <v>-0.029058439297228296</v>
+        <v>-0.0052248274436115568</v>
       </c>
       <c r="X31" s="8">
-        <v>28.106944736842102</v>
+        <v>27.117836491228072</v>
       </c>
       <c r="Y31" s="6">
-        <v>0.74672489082969429</v>
+        <v>0.79790940766550522</v>
       </c>
       <c r="Z31" s="6">
-        <v>0.11403508771929824</v>
+        <v>0.094736842105263161</v>
       </c>
       <c r="AA31" s="8">
-        <v>3.3007228915662647</v>
+        <v>3.271647509578544</v>
       </c>
       <c r="AB31" s="8">
-        <v>9.0296375565610862</v>
+        <v>8.3274575539568332</v>
       </c>
       <c r="AC31" s="8">
-        <v>12.410968</v>
+        <v>11.603024</v>
       </c>
       <c r="AD31" s="8">
-        <v>18.93845043859649</v>
+        <v>18.233742807017542</v>
       </c>
       <c r="AE31" s="6">
-        <v>0.66228070175438591</v>
+        <v>0.69824561403508767</v>
       </c>
       <c r="AF31" s="9"/>
       <c r="AG31" s="5">
-        <v>2022</v>
+        <v>2659.1999999999998</v>
       </c>
       <c r="AH31" s="10">
         <v>3</v>
@@ -5832,7 +5832,7 @@
         <v>19601</v>
       </c>
       <c r="B35" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C35" s="4">
         <v>44</v>
@@ -5869,55 +5869,55 @@
         <v>52</v>
       </c>
       <c r="O35" s="5">
-        <v>36940.809999999998</v>
+        <v>51976.509999999995</v>
       </c>
       <c r="P35" s="5">
-        <v>43097.611666666664</v>
+        <v>51976.509999999995</v>
       </c>
       <c r="Q35" s="6">
-        <v>-0.090276358821079317</v>
+        <v>0.097143393900502861</v>
       </c>
       <c r="R35" s="7">
-        <v>488.83333333333331</v>
+        <v>577</v>
       </c>
       <c r="S35" s="6">
-        <v>-0.087145969498910736</v>
+        <v>-0.10819165378670792</v>
       </c>
       <c r="T35" s="6">
-        <v>0.26464061832970098</v>
+        <v>0.2556435089620292</v>
       </c>
       <c r="U35" s="6">
-        <v>-0.040285830224080089</v>
+        <v>-0.052469713722602764</v>
       </c>
       <c r="V35" s="6">
-        <v>0.070635037510005882</v>
+        <v>0.059454270785014231</v>
       </c>
       <c r="W35" s="6">
-        <v>0.034235456667030317</v>
+        <v>0.028361956199059922</v>
       </c>
       <c r="X35" s="8">
-        <v>22.835027235772358</v>
+        <v>23.41641280487805</v>
       </c>
       <c r="Y35" s="6">
-        <v>0.84552845528455289</v>
+        <v>0.87804878048780488</v>
       </c>
       <c r="Z35" s="6">
-        <v>0.02032520325203252</v>
+        <v>0.018292682926829267</v>
       </c>
       <c r="AA35" s="8">
-        <v>2.6629020304568525</v>
+        <v>3.0301459016393442</v>
       </c>
       <c r="AB35" s="8">
-        <v>6.0520306722689075</v>
+        <v>6.5262053459119489</v>
       </c>
       <c r="AC35" s="8">
-        <v>8.7674029999999998</v>
+        <v>9.5343420000000005</v>
       </c>
       <c r="AD35" s="8">
-        <v>16.405758943089431</v>
+        <v>17.175864024390243</v>
       </c>
       <c r="AE35" s="6">
-        <v>0.88211382113821135</v>
+        <v>0.85365853658536583</v>
       </c>
       <c r="AF35" s="9"/>
       <c r="AG35" s="5">
@@ -6266,7 +6266,7 @@
         <v>3.6358402439024391</v>
       </c>
       <c r="AC38" s="8">
-        <v>6.9058109999999999</v>
+        <v>7.5871890000000004</v>
       </c>
       <c r="AD38" s="8">
         <v>14.496558704453442</v>
@@ -6449,7 +6449,7 @@
         <v>19615</v>
       </c>
       <c r="B40" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C40" s="4">
         <v>44</v>
@@ -6486,59 +6486,59 @@
         <v>52</v>
       </c>
       <c r="O40" s="5">
-        <v>35546.860000000001</v>
+        <v>45697.510000000002</v>
       </c>
       <c r="P40" s="5">
-        <v>41471.33666666667</v>
+        <v>45697.510000000002</v>
       </c>
       <c r="Q40" s="6">
-        <v>0.13127700517410013</v>
+        <v>0.24656079142646781</v>
       </c>
       <c r="R40" s="7">
-        <v>490</v>
+        <v>551</v>
       </c>
       <c r="S40" s="6">
-        <v>0.13207547169811318</v>
+        <v>0.17735042735042739</v>
       </c>
       <c r="T40" s="6">
         <v>0</v>
       </c>
       <c r="U40" s="6">
-        <v>-0.33471648410014276</v>
+        <v>-0.32909167260973299</v>
       </c>
       <c r="V40" s="6">
-        <v>0.090000523252968048</v>
+        <v>0.093908858491414518</v>
       </c>
       <c r="W40" s="6">
-        <v>0.056497423401110532</v>
+        <v>0.060328691869644541</v>
       </c>
       <c r="X40" s="8">
-        <v>27.878963719512196</v>
+        <v>31.49468845265589</v>
       </c>
       <c r="Y40" s="6">
-        <v>0.18318318318318319</v>
+        <v>0.1367713004484305</v>
       </c>
       <c r="Z40" s="6">
-        <v>0.082317073170731711</v>
+        <v>0.19861431870669746</v>
       </c>
       <c r="AA40" s="8">
-        <v>2.8418979166666669</v>
+        <v>2.9595780316344467</v>
       </c>
       <c r="AB40" s="8">
-        <v>10.135905787781351</v>
+        <v>12.909495192307693</v>
       </c>
       <c r="AC40" s="8">
-        <v>12.964057</v>
+        <v>15.853987999999999</v>
       </c>
       <c r="AD40" s="8">
-        <v>19.208536585365852</v>
+        <v>22.123787528868363</v>
       </c>
       <c r="AE40" s="6">
-        <v>0.68292682926829273</v>
+        <v>0.54734411085450352</v>
       </c>
       <c r="AF40" s="9"/>
       <c r="AG40" s="5">
-        <v>-139.59999999999999</v>
+        <v>-434</v>
       </c>
       <c r="AH40" s="10">
         <v>2</v>
@@ -7197,7 +7197,7 @@
         <v>19624</v>
       </c>
       <c r="B46" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C46" s="4">
         <v>44</v>
@@ -7232,59 +7232,59 @@
         <v>52</v>
       </c>
       <c r="O46" s="5">
-        <v>19742.879999999997</v>
+        <v>28066.539999999997</v>
       </c>
       <c r="P46" s="5">
-        <v>23033.359999999997</v>
+        <v>28066.539999999997</v>
       </c>
       <c r="Q46" s="6">
-        <v>-0.166165521865142</v>
+        <v>0.016041460470861413</v>
       </c>
       <c r="R46" s="7">
-        <v>276.5</v>
+        <v>331</v>
       </c>
       <c r="S46" s="6">
-        <v>-0.12867647058823539</v>
+        <v>-0.12664907651715041</v>
       </c>
       <c r="T46" s="6">
-        <v>0.28591661398944834</v>
+        <v>0.27157580877443388</v>
       </c>
       <c r="U46" s="6">
-        <v>-0.049856079761412715</v>
+        <v>-0.064009553724826779</v>
       </c>
       <c r="V46" s="6">
-        <v>0.038122553548418467</v>
+        <v>0.034802259202594978</v>
       </c>
       <c r="W46" s="6">
-        <v>-0.019393877691603251</v>
+        <v>-0.012713038372382203</v>
       </c>
       <c r="X46" s="8">
-        <v>22.03318181818182</v>
+        <v>23.136305732484075</v>
       </c>
       <c r="Y46" s="6">
-        <v>0.96363636363636362</v>
+        <v>0.93630573248407645</v>
       </c>
       <c r="Z46" s="6">
-        <v>0</v>
+        <v>0.012738853503184714</v>
       </c>
       <c r="AA46" s="8">
-        <v>2.5236170212765954</v>
+        <v>2.6206948640483385</v>
       </c>
       <c r="AB46" s="8">
-        <v>5.3781660000000002</v>
+        <v>5.8083328767123295</v>
       </c>
       <c r="AC46" s="8">
-        <v>7.8692260000000003</v>
+        <v>8.4022819999999996</v>
       </c>
       <c r="AD46" s="8">
-        <v>13.954091818181819</v>
+        <v>14.670807643312102</v>
       </c>
       <c r="AE46" s="6">
-        <v>0.84545454545454546</v>
+        <v>0.82165605095541405</v>
       </c>
       <c r="AF46" s="9"/>
       <c r="AG46" s="5">
-        <v>-265.5</v>
+        <v>-565.84000000000003</v>
       </c>
       <c r="AH46" s="10">
         <v>3</v>
@@ -8070,7 +8070,7 @@
         <v>19647</v>
       </c>
       <c r="B53" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C53" s="4">
         <v>44</v>
@@ -8105,55 +8105,55 @@
         <v>52</v>
       </c>
       <c r="O53" s="5">
-        <v>25672.68</v>
+        <v>33502.190000000002</v>
       </c>
       <c r="P53" s="5">
-        <v>29951.460000000003</v>
+        <v>33502.190000000002</v>
       </c>
       <c r="Q53" s="6">
-        <v>-0.15408919334544946</v>
+        <v>-0.053806907322914488</v>
       </c>
       <c r="R53" s="7">
-        <v>312.66666666666663</v>
+        <v>350</v>
       </c>
       <c r="S53" s="6">
-        <v>-0.27371273712737132</v>
+        <v>-0.23245614035087714</v>
       </c>
       <c r="T53" s="6">
-        <v>-0.00015995992627181892</v>
+        <v>3.756769333586849E-05</v>
       </c>
       <c r="U53" s="6">
-        <v>-0.38738404404993948</v>
+        <v>-0.38564408475983208</v>
       </c>
       <c r="V53" s="6">
-        <v>0.024932048387624511</v>
+        <v>0.038929753547454655</v>
       </c>
       <c r="W53" s="6">
-        <v>-0.01894221795309255</v>
+        <v>-0.00059154341850487988</v>
       </c>
       <c r="X53" s="8">
-        <v>29.736403684210526</v>
+        <v>32.517507142857141</v>
       </c>
       <c r="Y53" s="6">
-        <v>0.68421052631578949</v>
+        <v>0.65546218487394958</v>
       </c>
       <c r="Z53" s="6">
-        <v>0.16315789473684211</v>
+        <v>0.22268907563025211</v>
       </c>
       <c r="AA53" s="8">
-        <v>4.6347377289377292</v>
+        <v>6.7962293296089387</v>
       </c>
       <c r="AB53" s="8">
-        <v>8.8296494736842099</v>
+        <v>9.9695382352941184</v>
       </c>
       <c r="AC53" s="8">
-        <v>13.526885</v>
+        <v>16.269262999999999</v>
       </c>
       <c r="AD53" s="8">
-        <v>21.511403157894737</v>
+        <v>24.087534873949579</v>
       </c>
       <c r="AE53" s="6">
-        <v>0.63684210526315788</v>
+        <v>0.57563025210084029</v>
       </c>
       <c r="AF53" s="9"/>
       <c r="AG53" s="5">
@@ -8199,7 +8199,7 @@
         <v>19648</v>
       </c>
       <c r="B54" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C54" s="4">
         <v>44</v>
@@ -8236,59 +8236,59 @@
         <v>52</v>
       </c>
       <c r="O54" s="5">
-        <v>28523.099999999999</v>
+        <v>38383.399999999994</v>
       </c>
       <c r="P54" s="5">
-        <v>33276.949999999997</v>
+        <v>38383.399999999987</v>
       </c>
       <c r="Q54" s="6">
-        <v>-0.04762538482694989</v>
+        <v>0.098519419719452994</v>
       </c>
       <c r="R54" s="7">
-        <v>378</v>
+        <v>429</v>
       </c>
       <c r="S54" s="6">
-        <v>-0.018181818181818188</v>
+        <v>-0.033783783783783772</v>
       </c>
       <c r="T54" s="6">
-        <v>0.35020045857568077</v>
+        <v>0.34972596487023033</v>
       </c>
       <c r="U54" s="6">
-        <v>-0.0044426201920548612</v>
+        <v>-0.0032234872366700184</v>
       </c>
       <c r="V54" s="6">
-        <v>0.007958917508966417</v>
+        <v>0.014136540796281726</v>
       </c>
       <c r="W54" s="6">
-        <v>-0.0072831143879872806</v>
+        <v>-0.00018814122771823236</v>
       </c>
       <c r="X54" s="8">
-        <v>28.319397740112997</v>
+        <v>30.913472500000001</v>
       </c>
       <c r="Y54" s="6">
-        <v>0.8314606741573034</v>
+        <v>0.74273858921161828</v>
       </c>
       <c r="Z54" s="6">
-        <v>0.12994350282485875</v>
+        <v>0.19166666666666668</v>
       </c>
       <c r="AA54" s="8">
-        <v>6.2680731249999999</v>
+        <v>5.9278040000000001</v>
       </c>
       <c r="AB54" s="8">
-        <v>6.2542387283237</v>
+        <v>8.2714893617021268</v>
       </c>
       <c r="AC54" s="8">
-        <v>12.979238</v>
+        <v>14.694534000000001</v>
       </c>
       <c r="AD54" s="8">
-        <v>19.673969662921351</v>
+        <v>21.347441078838173</v>
       </c>
       <c r="AE54" s="6">
-        <v>0.64406779661016944</v>
+        <v>0.54583333333333328</v>
       </c>
       <c r="AF54" s="9"/>
       <c r="AG54" s="5">
-        <v>-438.10000000000002</v>
+        <v>-495.12</v>
       </c>
       <c r="AH54" s="10">
         <v>2</v>
@@ -8330,7 +8330,7 @@
         <v>19649</v>
       </c>
       <c r="B55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C55" s="4">
         <v>44</v>
@@ -8365,59 +8365,59 @@
         <v>52</v>
       </c>
       <c r="O55" s="5">
-        <v>41386.68</v>
+        <v>55698.099999999999</v>
       </c>
       <c r="P55" s="5">
-        <v>48284.459999999999</v>
+        <v>55698.099999999999</v>
       </c>
       <c r="Q55" s="6">
-        <v>-0.038149161954305177</v>
+        <v>0.10953429245253887</v>
       </c>
       <c r="R55" s="7">
-        <v>534.33333333333326</v>
+        <v>624</v>
       </c>
       <c r="S55" s="6">
-        <v>-0.11240310077519389</v>
+        <v>-0.093023255813953543</v>
       </c>
       <c r="T55" s="6">
-        <v>0.2757349466060095</v>
+        <v>0.27394769300927679</v>
       </c>
       <c r="U55" s="6">
-        <v>-0.050546359360064637</v>
+        <v>-0.051820690472385952</v>
       </c>
       <c r="V55" s="6">
-        <v>0.043908293682895075</v>
+        <v>0.038131192985038989</v>
       </c>
       <c r="W55" s="6">
-        <v>0.0066888308025673969</v>
+        <v>0.006502106894131038</v>
       </c>
       <c r="X55" s="8">
-        <v>25.569162032085561</v>
+        <v>26.115769230769232</v>
       </c>
       <c r="Y55" s="6">
-        <v>0.97860962566844922</v>
+        <v>0.98461538461538467</v>
       </c>
       <c r="Z55" s="6">
-        <v>0.064171122994652413</v>
+        <v>0.08461538461538462</v>
       </c>
       <c r="AA55" s="8">
-        <v>2.2450452702702703</v>
+        <v>3.2038294214876033</v>
       </c>
       <c r="AB55" s="8">
-        <v>7.2728364640883978</v>
+        <v>7.2039844621513947</v>
       </c>
       <c r="AC55" s="8">
-        <v>9.5528890000000004</v>
+        <v>10.283261</v>
       </c>
       <c r="AD55" s="8">
-        <v>17.078877005347593</v>
+        <v>17.771153846153847</v>
       </c>
       <c r="AE55" s="6">
-        <v>0.73262032085561501</v>
+        <v>0.7153846153846154</v>
       </c>
       <c r="AF55" s="9"/>
       <c r="AG55" s="5">
-        <v>-160.30000000000001</v>
+        <v>-389.5</v>
       </c>
       <c r="AH55" s="10">
         <v>5</v>
@@ -8588,7 +8588,7 @@
         <v>19654</v>
       </c>
       <c r="B57" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c t="s" r="C57" s="4">
         <v>44</v>
@@ -8623,59 +8623,59 @@
         <v>52</v>
       </c>
       <c r="O57" s="5">
-        <v>20924.129999999997</v>
+        <v>38354.859999999993</v>
       </c>
       <c r="P57" s="5">
-        <v>29293.781999999996</v>
+        <v>38354.859999999993</v>
       </c>
       <c r="Q57" s="6">
-        <v>-0.18343970847348601</v>
+        <v>0.069136640091697066</v>
       </c>
       <c r="R57" s="7">
-        <v>352.80000000000001</v>
+        <v>462</v>
       </c>
       <c r="S57" s="6">
-        <v>-0.015625000000000111</v>
+        <v>-0.085148514851485113</v>
       </c>
       <c r="T57" s="6">
-        <v>0.28859185543198207</v>
+        <v>0.27676211306728793</v>
       </c>
       <c r="U57" s="6">
-        <v>-0.04254210330369769</v>
+        <v>-0.045864537114722881</v>
       </c>
       <c r="V57" s="6">
-        <v>0.05998077339416262</v>
+        <v>0.053991045724062083</v>
       </c>
       <c r="W57" s="6">
-        <v>0.012947993536648834</v>
+        <v>0.01357739279976514</v>
       </c>
       <c r="X57" s="8">
-        <v>22.911112037037036</v>
+        <v>24.027222380952381</v>
       </c>
       <c r="Y57" s="6">
-        <v>0.96296296296296291</v>
+        <v>0.97142857142857142</v>
       </c>
       <c r="Z57" s="6">
-        <v>0.0092592592592592587</v>
+        <v>0.023809523809523808</v>
       </c>
       <c r="AA57" s="8">
-        <v>3.5140004</v>
+        <v>3.6241687361419066</v>
       </c>
       <c r="AB57" s="8">
-        <v>5.2138895833333327</v>
+        <v>5.4694876923076921</v>
       </c>
       <c r="AC57" s="8">
-        <v>8.5376969999999996</v>
+        <v>8.9540600000000001</v>
       </c>
       <c r="AD57" s="8">
-        <v>15.308795370370369</v>
+        <v>16.126983809523811</v>
       </c>
       <c r="AE57" s="6">
-        <v>0.77777777777777779</v>
+        <v>0.80000000000000004</v>
       </c>
       <c r="AF57" s="9"/>
       <c r="AG57" s="5">
-        <v>-75.799999999999997</v>
+        <v>-142.69999999999999</v>
       </c>
       <c r="AH57" s="10">
         <v>4</v>
@@ -8808,7 +8808,7 @@
         <v>19657</v>
       </c>
       <c r="B59" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C59" s="4">
         <v>44</v>
@@ -8845,59 +8845,59 @@
         <v>52</v>
       </c>
       <c r="O59" s="5">
-        <v>29308.270000000004</v>
+        <v>37571.270000000004</v>
       </c>
       <c r="P59" s="5">
-        <v>34192.981666666667</v>
+        <v>37571.270000000004</v>
       </c>
       <c r="Q59" s="6">
-        <v>0.20472354434298512</v>
+        <v>0.32375099665532514</v>
       </c>
       <c r="R59" s="7">
-        <v>357</v>
+        <v>390</v>
       </c>
       <c r="S59" s="6">
-        <v>0.092857142857142971</v>
+        <v>0.11111111111111116</v>
       </c>
       <c r="T59" s="6">
         <v>0</v>
       </c>
       <c r="U59" s="6">
-        <v>-0.32417914806981096</v>
+        <v>-0.32220923061690487</v>
       </c>
       <c r="V59" s="6">
-        <v>0.052476229405556858</v>
+        <v>0.048998476761631965</v>
       </c>
       <c r="W59" s="6">
-        <v>0.02837757056284796</v>
+        <v>0.026842984014115043</v>
       </c>
       <c r="X59" s="8">
-        <v>23.12371794871795</v>
+        <v>24.202042647058825</v>
       </c>
       <c r="Y59" s="6">
-        <v>0.84713375796178347</v>
+        <v>0.82926829268292679</v>
       </c>
       <c r="Z59" s="6">
-        <v>0.02564102564102564</v>
+        <v>0.034313725490196081</v>
       </c>
       <c r="AA59" s="8">
-        <v>5.791216216216216</v>
+        <v>6.1220316622691291</v>
       </c>
       <c r="AB59" s="8">
-        <v>5.8300006451612898</v>
+        <v>6.2451326732673271</v>
       </c>
       <c r="AC59" s="8">
-        <v>11.596074</v>
+        <v>12.410341000000001</v>
       </c>
       <c r="AD59" s="8">
-        <v>18.452992307692309</v>
+        <v>19.215686764705882</v>
       </c>
       <c r="AE59" s="6">
-        <v>0.87179487179487181</v>
+        <v>0.81862745098039214</v>
       </c>
       <c r="AF59" s="9"/>
       <c r="AG59" s="5">
-        <v>-1750.0999999999999</v>
+        <v>-1979.5</v>
       </c>
       <c r="AH59" s="10">
         <v>3</v>
@@ -9814,7 +9814,7 @@
         <v>19685</v>
       </c>
       <c r="B67" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C67" s="4">
         <v>44</v>
@@ -9851,55 +9851,55 @@
         <v>52</v>
       </c>
       <c r="O67" s="5">
-        <v>21543.639999999999</v>
+        <v>26353.790000000001</v>
       </c>
       <c r="P67" s="5">
-        <v>25134.246666666662</v>
+        <v>26353.790000000001</v>
       </c>
       <c r="Q67" s="6">
-        <v>-0.18576681403319861</v>
+        <v>-0.14625925819141194</v>
       </c>
       <c r="R67" s="7">
-        <v>281.16666666666663</v>
+        <v>292</v>
       </c>
       <c r="S67" s="6">
-        <v>-0.18855218855218869</v>
+        <v>-0.20652173913043481</v>
       </c>
       <c r="T67" s="6">
-        <v>0</v>
+        <v>-2.1932329277876158E-05</v>
       </c>
       <c r="U67" s="6">
-        <v>-0.32710860374569944</v>
+        <v>-0.3316118099142476</v>
       </c>
       <c r="V67" s="6">
-        <v>0.036151202860797899</v>
+        <v>0.032608839184041456</v>
       </c>
       <c r="W67" s="6">
-        <v>-0.015916135806205451</v>
+        <v>-0.014343800265540555</v>
       </c>
       <c r="X67" s="8">
-        <v>33.313919148936172</v>
+        <v>36.144444907407404</v>
       </c>
       <c r="Y67" s="6">
-        <v>0.44680851063829785</v>
+        <v>0.39814814814814814</v>
       </c>
       <c r="Z67" s="6">
-        <v>0.19680851063829788</v>
+        <v>0.24074074074074073</v>
       </c>
       <c r="AA67" s="8">
-        <v>7.1342138211382107</v>
+        <v>7.3023645270270263</v>
       </c>
       <c r="AB67" s="8">
-        <v>7.545269032258064</v>
+        <v>10.00288659217877</v>
       </c>
       <c r="AC67" s="8">
-        <v>15.073714000000001</v>
+        <v>17.650373999999999</v>
       </c>
       <c r="AD67" s="8">
-        <v>19.864349197860964</v>
+        <v>22.114495813953489</v>
       </c>
       <c r="AE67" s="6">
-        <v>0.42553191489361702</v>
+        <v>0.39814814814814814</v>
       </c>
       <c r="AF67" s="9"/>
       <c r="AG67" s="5">
@@ -9945,7 +9945,7 @@
         <v>19687</v>
       </c>
       <c r="B68" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C68" s="4">
         <v>44</v>
@@ -9982,59 +9982,59 @@
         <v>52</v>
       </c>
       <c r="O68" s="5">
-        <v>29593.209999999999</v>
+        <v>34514.839999999997</v>
       </c>
       <c r="P68" s="5">
-        <v>34525.411666666667</v>
+        <v>34514.839999999997</v>
       </c>
       <c r="Q68" s="6">
-        <v>0.59940498057188152</v>
+        <v>0.59891524343325275</v>
       </c>
       <c r="R68" s="7">
-        <v>442.16666666666663</v>
+        <v>446</v>
       </c>
       <c r="S68" s="6">
-        <v>0.36823104693140807</v>
+        <v>0.40694006309148256</v>
       </c>
       <c r="T68" s="6">
         <v>0</v>
       </c>
       <c r="U68" s="6">
-        <v>-0.31448328856518099</v>
+        <v>-0.3144760340769362</v>
       </c>
       <c r="V68" s="6">
-        <v>0.022413114359679128</v>
+        <v>0.02112078456687037</v>
       </c>
       <c r="W68" s="6">
-        <v>0.01545949222811584</v>
+        <v>0.014249247570030748</v>
       </c>
       <c r="X68" s="8">
-        <v>36.886325641025643</v>
+        <v>36.523668000000001</v>
       </c>
       <c r="Y68" s="6">
-        <v>0.79487179487179482</v>
+        <v>0.83999999999999997</v>
       </c>
       <c r="Z68" s="6">
-        <v>0.41025641025641024</v>
+        <v>0.40000000000000002</v>
       </c>
       <c r="AA68" s="8">
-        <v>6.1386885885885887</v>
+        <v>6.1113966580976857</v>
       </c>
       <c r="AB68" s="8">
-        <v>11.38225806451613</v>
+        <v>10.090171794871795</v>
       </c>
       <c r="AC68" s="8">
-        <v>18.953198</v>
+        <v>17.263169999999999</v>
       </c>
       <c r="AD68" s="8">
-        <v>22.46709487179487</v>
+        <v>20.849668000000001</v>
       </c>
       <c r="AE68" s="6">
-        <v>0.4358974358974359</v>
+        <v>0.40000000000000002</v>
       </c>
       <c r="AF68" s="9"/>
       <c r="AG68" s="5">
-        <v>-1495.1800000000001</v>
+        <v>-1688.48</v>
       </c>
       <c r="AH68" s="10">
         <v>3</v>
@@ -10207,7 +10207,7 @@
         <v>19689</v>
       </c>
       <c r="B70" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C70" s="4">
         <v>44</v>
@@ -10244,34 +10244,34 @@
         <v>52</v>
       </c>
       <c r="O70" s="5">
-        <v>32920.07</v>
+        <v>44123.419999999998</v>
       </c>
       <c r="P70" s="5">
-        <v>38406.748333333329</v>
+        <v>44123.419999999998</v>
       </c>
       <c r="Q70" s="6">
-        <v>-0.15091853072519534</v>
+        <v>-0.02453657472184767</v>
       </c>
       <c r="R70" s="7">
-        <v>360.5</v>
+        <v>416</v>
       </c>
       <c r="S70" s="6">
-        <v>-0.20360824742268047</v>
+        <v>-0.18271119842829064</v>
       </c>
       <c r="T70" s="6">
-        <v>0.48712134269459328</v>
+        <v>0.36624923226712708</v>
       </c>
       <c r="U70" s="6">
-        <v>0.1825982964191753</v>
+        <v>0.06365074828741743</v>
       </c>
       <c r="V70" s="6">
-        <v>0.0044268131872137574</v>
+        <v>0.0033028038171111851</v>
       </c>
       <c r="W70" s="6">
-        <v>-0.018109590896981689</v>
+        <v>-0.016580514384424417</v>
       </c>
       <c r="X70" s="8">
-        <v>15.025301204819277</v>
+        <v>15.516891891891891</v>
       </c>
       <c r="Y70" s="6">
         <v>1</v>
@@ -10280,19 +10280,19 @@
         <v>0</v>
       </c>
       <c r="AA70" s="8">
-        <v>3.260664308681672</v>
+        <v>3.4512329355608595</v>
       </c>
       <c r="AB70" s="8">
-        <v>2.8380715686274507</v>
+        <v>2.9029338028169014</v>
       </c>
       <c r="AC70" s="8">
-        <v>6.2948570000000004</v>
+        <v>6.4849220000000001</v>
       </c>
       <c r="AD70" s="8">
-        <v>10.685039759036144</v>
+        <v>11.006155855855855</v>
       </c>
       <c r="AE70" s="6">
-        <v>0.98795180722891562</v>
+        <v>0.99099099099099097</v>
       </c>
       <c r="AF70" s="9"/>
       <c r="AG70" s="5">
@@ -10596,7 +10596,7 @@
         <v>19694</v>
       </c>
       <c r="B73" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C73" s="4">
         <v>44</v>
@@ -10633,59 +10633,59 @@
         <v>52</v>
       </c>
       <c r="O73" s="5">
-        <v>42120.160000000003</v>
+        <v>49657.710000000006</v>
       </c>
       <c r="P73" s="5">
-        <v>49140.186666666668</v>
+        <v>49657.710000000006</v>
       </c>
       <c r="Q73" s="6">
-        <v>0.33671218652169088</v>
+        <v>0.35078986496374798</v>
       </c>
       <c r="R73" s="7">
-        <v>488.83333333333331</v>
+        <v>499.00000000000006</v>
       </c>
       <c r="S73" s="6">
-        <v>0.077120822622108065</v>
+        <v>0.020449897750511425</v>
       </c>
       <c r="T73" s="6">
-        <v>0.25146712643066882</v>
+        <v>0.29059230480020121</v>
       </c>
       <c r="U73" s="6">
-        <v>-0.21532929599507694</v>
+        <v>-0.16232266046903895</v>
       </c>
       <c r="V73" s="6">
-        <v>0.10587992780654204</v>
+        <v>0.10205460541776896</v>
       </c>
       <c r="W73" s="6">
-        <v>0.071012064056736712</v>
+        <v>0.067842596849512396</v>
       </c>
       <c r="X73" s="8">
-        <v>35.675171232876714</v>
+        <v>36.060019364161853</v>
       </c>
       <c r="Y73" s="6">
-        <v>0.4452054794520548</v>
+        <v>0.430635838150289</v>
       </c>
       <c r="Z73" s="6">
-        <v>0.29452054794520549</v>
+        <v>0.30057803468208094</v>
       </c>
       <c r="AA73" s="8">
-        <v>7.1830949880668262</v>
+        <v>6.6024818913480887</v>
       </c>
       <c r="AB73" s="8">
-        <v>15.531436896551723</v>
+        <v>16.204699709302325</v>
       </c>
       <c r="AC73" s="8">
-        <v>22.782382999999999</v>
+        <v>22.894027999999999</v>
       </c>
       <c r="AD73" s="8">
-        <v>29.598230479452056</v>
+        <v>29.708670520231216</v>
       </c>
       <c r="AE73" s="6">
-        <v>0.49657534246575341</v>
+        <v>0.48265895953757226</v>
       </c>
       <c r="AF73" s="9"/>
       <c r="AG73" s="5">
-        <v>-1762.5999999999999</v>
+        <v>-2063.25</v>
       </c>
       <c r="AH73" s="10">
         <v>2</v>
@@ -12741,7 +12741,7 @@
         <v>19730</v>
       </c>
       <c r="B90" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C90" s="4">
         <v>44</v>
@@ -12776,55 +12776,55 @@
         <v>52</v>
       </c>
       <c r="O90" s="5">
-        <v>49487.059999999998</v>
+        <v>62360.949999999997</v>
       </c>
       <c r="P90" s="5">
-        <v>57734.903333333328</v>
+        <v>62360.949999999997</v>
       </c>
       <c r="Q90" s="6">
-        <v>-0.015781726779913519</v>
+        <v>0.063079402263901851</v>
       </c>
       <c r="R90" s="7">
-        <v>585.66666666666674</v>
+        <v>640</v>
       </c>
       <c r="S90" s="6">
-        <v>-0.061682242990654168</v>
+        <v>-0.09219858156028371</v>
       </c>
       <c r="T90" s="6">
-        <v>0.0092755560746587088</v>
+        <v>0.01804205997503245</v>
       </c>
       <c r="U90" s="6">
-        <v>-0.32319418449994808</v>
+        <v>-0.31428626408032589</v>
       </c>
       <c r="V90" s="6">
-        <v>0.019125565349810636</v>
+        <v>0.022291890999094784</v>
       </c>
       <c r="W90" s="6">
-        <v>0.0039971661278726195</v>
+        <v>0.0063798498900353509</v>
       </c>
       <c r="X90" s="8">
-        <v>28.794444666666664</v>
+        <v>30.211111111111109</v>
       </c>
       <c r="Y90" s="6">
-        <v>0.61333333333333329</v>
+        <v>0.56613756613756616</v>
       </c>
       <c r="Z90" s="6">
-        <v>0.16</v>
+        <v>0.20105820105820105</v>
       </c>
       <c r="AA90" s="8">
-        <v>6.4565013861386138</v>
+        <v>6.1405795031055899</v>
       </c>
       <c r="AB90" s="8">
-        <v>8.9715879194630865</v>
+        <v>10.114715957446808</v>
       </c>
       <c r="AC90" s="8">
-        <v>15.076995999999999</v>
+        <v>16.016908000000001</v>
       </c>
       <c r="AD90" s="8">
-        <v>22.940111333333334</v>
+        <v>23.887213756613757</v>
       </c>
       <c r="AE90" s="6">
-        <v>0.66000000000000003</v>
+        <v>0.59788359788359791</v>
       </c>
       <c r="AF90" s="9"/>
       <c r="AG90" s="5">
@@ -14005,7 +14005,7 @@
         <v>19749</v>
       </c>
       <c r="B100" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C100" s="4">
         <v>44</v>
@@ -14040,59 +14040,59 @@
         <v>52</v>
       </c>
       <c r="O100" s="5">
-        <v>25996.770000000004</v>
+        <v>31718.230000000003</v>
       </c>
       <c r="P100" s="5">
-        <v>30329.565000000002</v>
+        <v>31718.230000000003</v>
       </c>
       <c r="Q100" s="6">
-        <v>0.19158816268063661</v>
+        <v>0.246146042951221</v>
       </c>
       <c r="R100" s="7">
-        <v>323.16666666666663</v>
+        <v>342</v>
       </c>
       <c r="S100" s="6">
-        <v>0.077821011673151474</v>
+        <v>0.07547169811320753</v>
       </c>
       <c r="T100" s="6">
-        <v>0.38083080705795375</v>
+        <v>1.185806310755676</v>
       </c>
       <c r="U100" s="6">
-        <v>-2.5225283410208266</v>
+        <v>-1.8880691860800554</v>
       </c>
       <c r="V100" s="6">
-        <v>0.018056762436256504</v>
+        <v>0.016906302779190391</v>
       </c>
       <c r="W100" s="6">
-        <v>0.0071450222469945307</v>
+        <v>0.0063133409398948171</v>
       </c>
       <c r="X100" s="8">
-        <v>38.805482894736841</v>
+        <v>40.132373821989532</v>
       </c>
       <c r="Y100" s="6">
-        <v>0.82894736842105265</v>
+        <v>0.74869109947643975</v>
       </c>
       <c r="Z100" s="6">
-        <v>0.36842105263157893</v>
+        <v>0.41884816753926701</v>
       </c>
       <c r="AA100" s="8">
-        <v>9.1926340823970047</v>
+        <v>9.1982722560975603</v>
       </c>
       <c r="AB100" s="8">
-        <v>11.915667333333333</v>
+        <v>12.947884126984126</v>
       </c>
       <c r="AC100" s="8">
-        <v>21.455317000000001</v>
+        <v>22.298663999999999</v>
       </c>
       <c r="AD100" s="8">
-        <v>29.167873026315789</v>
+        <v>30.045637172774867</v>
       </c>
       <c r="AE100" s="6">
-        <v>0.38815789473684209</v>
+        <v>0.32460732984293195</v>
       </c>
       <c r="AF100" s="9"/>
       <c r="AG100" s="5">
-        <v>-669.29999999999995</v>
+        <v>-808.5</v>
       </c>
       <c r="AH100" s="10">
         <v>1</v>
@@ -14134,7 +14134,7 @@
         <v>19752</v>
       </c>
       <c r="B101" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C101" s="4">
         <v>44</v>
@@ -14169,59 +14169,59 @@
         <v>52</v>
       </c>
       <c r="O101" s="5">
-        <v>21974.909999999996</v>
+        <v>27214.859999999997</v>
       </c>
       <c r="P101" s="5">
-        <v>25637.394999999993</v>
+        <v>27214.859999999997</v>
       </c>
       <c r="Q101" s="6">
-        <v>0.50000058508307288</v>
+        <v>0.59229539206124171</v>
       </c>
       <c r="R101" s="7">
-        <v>283.5</v>
+        <v>301</v>
       </c>
       <c r="S101" s="6">
-        <v>0.40462427745664753</v>
+        <v>0.32017543859649122</v>
       </c>
       <c r="T101" s="6">
         <v>0</v>
       </c>
       <c r="U101" s="6">
-        <v>-0.29776231165451872</v>
+        <v>-0.30365542942348411</v>
       </c>
       <c r="V101" s="6">
-        <v>0.024482694127074923</v>
+        <v>0.039014751499732131</v>
       </c>
       <c r="W101" s="6">
-        <v>-0.03305656314405838</v>
+        <v>-0.014992507769652315</v>
       </c>
       <c r="X101" s="8">
-        <v>31.634023448275862</v>
+        <v>32.702083928571426</v>
       </c>
       <c r="Y101" s="6">
-        <v>0.43448275862068964</v>
+        <v>0.40828402366863903</v>
       </c>
       <c r="Z101" s="6">
-        <v>0.19310344827586207</v>
+        <v>0.22023809523809523</v>
       </c>
       <c r="AA101" s="8">
-        <v>6.1071224066390037</v>
+        <v>6.7369558528428088</v>
       </c>
       <c r="AB101" s="8">
-        <v>10.134543548387096</v>
+        <v>9.8377557823129251</v>
       </c>
       <c r="AC101" s="8">
-        <v>16.566132</v>
+        <v>16.639880000000002</v>
       </c>
       <c r="AD101" s="8">
-        <v>22.256134027777776</v>
+        <v>22.611177245508983</v>
       </c>
       <c r="AE101" s="6">
-        <v>0.58620689655172409</v>
+        <v>0.5535714285714286</v>
       </c>
       <c r="AF101" s="9"/>
       <c r="AG101" s="5">
-        <v>-906</v>
+        <v>-1102.2</v>
       </c>
       <c r="AH101" s="10">
         <v>2</v>
@@ -14394,7 +14394,7 @@
         <v>19754</v>
       </c>
       <c r="B103" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C103" s="4">
         <v>44</v>
@@ -14431,55 +14431,55 @@
         <v>52</v>
       </c>
       <c r="O103" s="5">
-        <v>52816.600000000006</v>
+        <v>66790.630000000005</v>
       </c>
       <c r="P103" s="5">
-        <v>61619.366666666676</v>
+        <v>66790.630000000005</v>
       </c>
       <c r="Q103" s="6">
-        <v>-0.0050552389471645309</v>
+        <v>0.078443207074804899</v>
       </c>
       <c r="R103" s="7">
-        <v>614.83333333333326</v>
+        <v>673</v>
       </c>
       <c r="S103" s="6">
-        <v>0.029296875</v>
+        <v>0.0029806259314455463</v>
       </c>
       <c r="T103" s="6">
-        <v>0.28990206109442868</v>
+        <v>0.29251418200427215</v>
       </c>
       <c r="U103" s="6">
-        <v>-0.029974076332062269</v>
+        <v>-0.029437415098495099</v>
       </c>
       <c r="V103" s="6">
-        <v>0.024705395652124523</v>
+        <v>0.024530738817705417</v>
       </c>
       <c r="W103" s="6">
-        <v>0.0010482499820132307</v>
+        <v>0.0024024851988969113</v>
       </c>
       <c r="X103" s="8">
-        <v>22.960710163934426</v>
+        <v>23.250467602040818</v>
       </c>
       <c r="Y103" s="6">
-        <v>0.9278688524590164</v>
+        <v>0.87755102040816324</v>
       </c>
       <c r="Z103" s="6">
-        <v>0.0032786885245901639</v>
+        <v>0.0076530612244897957</v>
       </c>
       <c r="AA103" s="8">
-        <v>2.547731379962193</v>
+        <v>2.5514747787610617</v>
       </c>
       <c r="AB103" s="8">
-        <v>4.9311950657894741</v>
+        <v>5.2410256410256411</v>
       </c>
       <c r="AC103" s="8">
-        <v>7.636768</v>
+        <v>7.93513</v>
       </c>
       <c r="AD103" s="8">
-        <v>15.558688852459015</v>
+        <v>15.842092091836733</v>
       </c>
       <c r="AE103" s="6">
-        <v>0.91147540983606556</v>
+        <v>0.89795918367346939</v>
       </c>
       <c r="AF103" s="9"/>
       <c r="AG103" s="5">
@@ -20777,10 +20777,10 @@
         <v>0.046762589928057485</v>
       </c>
       <c r="T152" s="6">
-        <v>-0.20105920497877766</v>
+        <v>0.17544145181954901</v>
       </c>
       <c r="U152" s="6">
-        <v>-0.50507466715525851</v>
+        <v>-0.12857367293164201</v>
       </c>
       <c r="V152" s="6">
         <v>0.032905646778482657</v>
@@ -20987,7 +20987,7 @@
         <v>19898</v>
       </c>
       <c r="B154" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c t="s" r="C154" s="4">
         <v>44</v>
@@ -21022,55 +21022,55 @@
         <v>52</v>
       </c>
       <c r="O154" s="5">
-        <v>7727.04</v>
+        <v>15389.32</v>
       </c>
       <c r="P154" s="5">
-        <v>13522.32</v>
+        <v>15389.319999999998</v>
       </c>
       <c r="Q154" s="6">
-        <v>-0.48089208285107188</v>
+        <v>-0.40921987857569253</v>
       </c>
       <c r="R154" s="7">
-        <v>155.75</v>
+        <v>184</v>
       </c>
       <c r="S154" s="6">
-        <v>-0.26446280991735538</v>
+        <v>-0.45074626865671641</v>
       </c>
       <c r="T154" s="6">
-        <v>0.00043742493891580736</v>
+        <v>0.00021963283627866599</v>
       </c>
       <c r="U154" s="6">
-        <v>-0.33871055410610013</v>
+        <v>-0.33942825284028144</v>
       </c>
       <c r="V154" s="6">
-        <v>0.099480719654615482</v>
+        <v>0.12903640316791126</v>
       </c>
       <c r="W154" s="6">
-        <v>0.031866212676522968</v>
+        <v>0.077289477377817856</v>
       </c>
       <c r="X154" s="8">
-        <v>24.240433333333335</v>
+        <v>28.208859459459457</v>
       </c>
       <c r="Y154" s="6">
-        <v>0.88888888888888884</v>
+        <v>0.65765765765765771</v>
       </c>
       <c r="Z154" s="6">
-        <v>0.018518518518518517</v>
+        <v>0.13513513513513514</v>
       </c>
       <c r="AA154" s="8">
-        <v>2.9956032967032966</v>
+        <v>3.4519752577319589</v>
       </c>
       <c r="AB154" s="8">
-        <v>6.6408792452830196</v>
+        <v>9.855351376146789</v>
       </c>
       <c r="AC154" s="8">
-        <v>9.4711259999999999</v>
+        <v>13.270580000000001</v>
       </c>
       <c r="AD154" s="8">
-        <v>16.260185185185183</v>
+        <v>19.926126126126128</v>
       </c>
       <c r="AE154" s="6">
-        <v>0.7592592592592593</v>
+        <v>0.59459459459459463</v>
       </c>
       <c r="AF154" s="9"/>
       <c r="AG154" s="5">
@@ -22515,7 +22515,7 @@
         <v>19927</v>
       </c>
       <c r="B166" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C166" s="4">
         <v>44</v>
@@ -22552,59 +22552,59 @@
         <v>52</v>
       </c>
       <c r="O166" s="5">
-        <v>9092.7399999999998</v>
+        <v>12048.09</v>
       </c>
       <c r="P166" s="5">
-        <v>10608.196666666667</v>
+        <v>12048.09</v>
       </c>
       <c r="Q166" s="6">
-        <v>-0.26310884317827965</v>
+        <v>-0.16308763340622445</v>
       </c>
       <c r="R166" s="7">
-        <v>142.33333333333331</v>
+        <v>160</v>
       </c>
       <c r="S166" s="6">
-        <v>-0.2129032258064516</v>
+        <v>-0.14438502673796794</v>
       </c>
       <c r="T166" s="6">
         <v>0</v>
       </c>
       <c r="U166" s="6">
-        <v>-0.3408444539269791</v>
+        <v>-0.34086232755565404</v>
       </c>
       <c r="V166" s="6">
-        <v>0.18654228538372372</v>
+        <v>0.1692057828253275</v>
       </c>
       <c r="W166" s="6">
-        <v>0.11048710289747644</v>
+        <v>0.10082564954279059</v>
       </c>
       <c r="X166" s="8">
-        <v>34.707304494382022</v>
+        <v>35.900000826446281</v>
       </c>
       <c r="Y166" s="6">
-        <v>0.6179775280898876</v>
+        <v>0.57024793388429751</v>
       </c>
       <c r="Z166" s="6">
-        <v>0.25842696629213485</v>
+        <v>0.33057851239669422</v>
       </c>
       <c r="AA166" s="8">
-        <v>7.4154572580645164</v>
+        <v>8.5958079754601222</v>
       </c>
       <c r="AB166" s="8">
-        <v>8.781418390804598</v>
+        <v>9.1209410256410255</v>
       </c>
       <c r="AC166" s="8">
-        <v>15.949827000000001</v>
+        <v>17.708169999999999</v>
       </c>
       <c r="AD166" s="8">
-        <v>22.433146067415731</v>
+        <v>24.063498347107441</v>
       </c>
       <c r="AE166" s="6">
-        <v>0.38202247191011235</v>
+        <v>0.33057851239669422</v>
       </c>
       <c r="AF166" s="9"/>
       <c r="AG166" s="5">
-        <v>-877.10000000000002</v>
+        <v>-980.89999999999998</v>
       </c>
       <c r="AH166" s="10">
         <v>1</v>
@@ -22648,7 +22648,7 @@
         <v>19928</v>
       </c>
       <c r="B167" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C167" s="4">
         <v>44</v>
@@ -22685,59 +22685,59 @@
         <v>52</v>
       </c>
       <c r="O167" s="5">
-        <v>23072.400000000001</v>
+        <v>27814.060000000001</v>
       </c>
       <c r="P167" s="5">
-        <v>26917.800000000003</v>
+        <v>27814.060000000001</v>
       </c>
       <c r="Q167" s="6">
-        <v>0.024564144023166534</v>
+        <v>0.058678219457347858</v>
       </c>
       <c r="R167" s="7">
-        <v>306.83333333333337</v>
+        <v>317</v>
       </c>
       <c r="S167" s="6">
-        <v>-0.096219931271477543</v>
+        <v>-0.1267217630853994</v>
       </c>
       <c r="T167" s="6">
-        <v>0.07022988505747127</v>
+        <v>0.066929171792970893</v>
       </c>
       <c r="U167" s="6">
-        <v>-0.28626185399004866</v>
+        <v>-0.28895127140733862</v>
       </c>
       <c r="V167" s="6">
-        <v>0.024396356685910441</v>
+        <v>0.024600777448527827</v>
       </c>
       <c r="W167" s="6">
-        <v>-0.009536827551533433</v>
+        <v>-0.0084785356758416419</v>
       </c>
       <c r="X167" s="8">
-        <v>27.453046236559139</v>
+        <v>25.84405782608696</v>
       </c>
       <c r="Y167" s="6">
-        <v>0.64516129032258063</v>
+        <v>0.63478260869565217</v>
       </c>
       <c r="Z167" s="6">
-        <v>0.13440860215053763</v>
+        <v>0.10869565217391304</v>
       </c>
       <c r="AA167" s="8">
-        <v>5.1864620689655174</v>
+        <v>4.9053268987341774</v>
       </c>
       <c r="AB167" s="8">
-        <v>7.6579545454545448</v>
+        <v>6.8995348837209303</v>
       </c>
       <c r="AC167" s="8">
-        <v>12.347954</v>
+        <v>11.369678</v>
       </c>
       <c r="AD167" s="8">
-        <v>18.707706451612903</v>
+        <v>17.65565260869565</v>
       </c>
       <c r="AE167" s="6">
-        <v>0.75806451612903225</v>
+        <v>0.79130434782608694</v>
       </c>
       <c r="AF167" s="9"/>
       <c r="AG167" s="5">
-        <v>-681</v>
+        <v>-953.5</v>
       </c>
       <c r="AH167" s="10">
         <v>4</v>
@@ -22779,7 +22779,7 @@
         <v>19930</v>
       </c>
       <c r="B168" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C168" s="4">
         <v>44</v>
@@ -22816,55 +22816,55 @@
         <v>52</v>
       </c>
       <c r="O168" s="5">
-        <v>27063.98</v>
+        <v>34377.979999999996</v>
       </c>
       <c r="P168" s="5">
-        <v>31574.64333333333</v>
+        <v>34377.979999999996</v>
       </c>
       <c r="Q168" s="6">
-        <v>0.23660644465593306</v>
+        <v>0.34639784125044537</v>
       </c>
       <c r="R168" s="7">
-        <v>393.16666666666663</v>
+        <v>422</v>
       </c>
       <c r="S168" s="6">
-        <v>-0.069060773480663196</v>
+        <v>-0.043083900226757343</v>
       </c>
       <c r="T168" s="6">
-        <v>0.41409679950990208</v>
+        <v>0.38719813962309596</v>
       </c>
       <c r="U168" s="6">
-        <v>0.12230084045288241</v>
+        <v>0.1020944191601717</v>
       </c>
       <c r="V168" s="6">
-        <v>0.071930384961857052</v>
+        <v>0.06987718591959155</v>
       </c>
       <c r="W168" s="6">
-        <v>0.040039657877370585</v>
+        <v>0.040212848457064666</v>
       </c>
       <c r="X168" s="8">
-        <v>28.003058426966291</v>
+        <v>27.970392058823531</v>
       </c>
       <c r="Y168" s="6">
-        <v>0.43071161048689138</v>
+        <v>0.39411764705882352</v>
       </c>
       <c r="Z168" s="6">
-        <v>0.074906367041198504</v>
+        <v>0.070588235294117646</v>
       </c>
       <c r="AA168" s="8">
-        <v>4.3374631268436579</v>
+        <v>4.4237983451536644</v>
       </c>
       <c r="AB168" s="8">
-        <v>10.639330681818182</v>
+        <v>10.24272997032641</v>
       </c>
       <c r="AC168" s="8">
-        <v>14.853928</v>
+        <v>14.588599</v>
       </c>
       <c r="AD168" s="8">
-        <v>21.61654194756554</v>
+        <v>21.392598235294116</v>
       </c>
       <c r="AE168" s="6">
-        <v>0.63670411985018727</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="AF168" s="9"/>
       <c r="AG168" s="5">
@@ -22910,7 +22910,7 @@
         <v>19931</v>
       </c>
       <c r="B169" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C169" s="4">
         <v>44</v>
@@ -22947,59 +22947,59 @@
         <v>52</v>
       </c>
       <c r="O169" s="5">
-        <v>24408.639999999999</v>
+        <v>34695.910000000003</v>
       </c>
       <c r="P169" s="5">
-        <v>28476.746666666662</v>
+        <v>34695.910000000003</v>
       </c>
       <c r="Q169" s="6">
-        <v>-0.15991899529622833</v>
+        <v>0.0235500309461254</v>
       </c>
       <c r="R169" s="7">
-        <v>326.66666666666663</v>
+        <v>388</v>
       </c>
       <c r="S169" s="6">
-        <v>-0.19075144508670527</v>
+        <v>-0.14912280701754388</v>
       </c>
       <c r="T169" s="6">
-        <v>0.18225470571076471</v>
+        <v>0.13039294833310322</v>
       </c>
       <c r="U169" s="6">
-        <v>-0.34138897128230006</v>
+        <v>-0.39768255105572958</v>
       </c>
       <c r="V169" s="6">
-        <v>0.087198549366126102</v>
+        <v>0.080127470356016015</v>
       </c>
       <c r="W169" s="6">
-        <v>0.058913892785505462</v>
+        <v>0.056237046383853309</v>
       </c>
       <c r="X169" s="8">
-        <v>24.571475</v>
+        <v>25.087582352941176</v>
       </c>
       <c r="Y169" s="6">
-        <v>0.76923076923076927</v>
+        <v>0.63398692810457513</v>
       </c>
       <c r="Z169" s="6">
-        <v>0.028846153846153848</v>
+        <v>0.039215686274509803</v>
       </c>
       <c r="AA169" s="8">
-        <v>4.5436512820512815</v>
+        <v>4.5624348167539273</v>
       </c>
       <c r="AB169" s="8">
-        <v>4.3039916666666667</v>
+        <v>4.515267132867133</v>
       </c>
       <c r="AC169" s="8">
-        <v>9.4284239999999997</v>
+        <v>9.6010120000000008</v>
       </c>
       <c r="AD169" s="8">
-        <v>15.745351923076923</v>
+        <v>15.975381045751632</v>
       </c>
       <c r="AE169" s="6">
-        <v>0.71153846153846156</v>
+        <v>0.71241830065359479</v>
       </c>
       <c r="AF169" s="9"/>
       <c r="AG169" s="5">
-        <v>-444</v>
+        <v>-754.79999999999995</v>
       </c>
       <c r="AH169" s="10">
         <v>2</v>
@@ -23434,7 +23434,7 @@
         <v>19943</v>
       </c>
       <c r="B173" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C173" s="4">
         <v>44</v>
@@ -23471,59 +23471,59 @@
         <v>52</v>
       </c>
       <c r="O173" s="5">
-        <v>14979.18</v>
+        <v>18915.139999999999</v>
       </c>
       <c r="P173" s="5">
-        <v>17475.710000000003</v>
+        <v>18915.139999999996</v>
       </c>
       <c r="Q173" s="6">
-        <v>0.0075841046299709447</v>
+        <v>0.090576257036226071</v>
       </c>
       <c r="R173" s="7">
-        <v>221.66666666666669</v>
+        <v>236.99999999999997</v>
       </c>
       <c r="S173" s="6">
-        <v>-0.030612244897959107</v>
+        <v>-0.052000000000000157</v>
       </c>
       <c r="T173" s="6">
-        <v>0.36484060542699936</v>
+        <v>0.36317539812023597</v>
       </c>
       <c r="U173" s="6">
-        <v>0.007552689800109218</v>
+        <v>0.0055290893961133783</v>
       </c>
       <c r="V173" s="6">
-        <v>0.066484079902905224</v>
+        <v>0.077861094340300946</v>
       </c>
       <c r="W173" s="6">
-        <v>0.019174414086752412</v>
+        <v>0.030846374914486489</v>
       </c>
       <c r="X173" s="8">
-        <v>25.322783486238531</v>
+        <v>25.779167424242424</v>
       </c>
       <c r="Y173" s="6">
-        <v>0.83486238532110091</v>
+        <v>0.77272727272727271</v>
       </c>
       <c r="Z173" s="6">
-        <v>0.03669724770642202</v>
+        <v>0.03787878787878788</v>
       </c>
       <c r="AA173" s="8">
-        <v>7.7055845744680846</v>
+        <v>7.4994323404255319</v>
       </c>
       <c r="AB173" s="8">
-        <v>6.8063504761904756</v>
+        <v>7.0165375000000001</v>
       </c>
       <c r="AC173" s="8">
-        <v>13.259254</v>
+        <v>13.466536</v>
       </c>
       <c r="AD173" s="8">
-        <v>19.814833027522937</v>
+        <v>20.07676893939394</v>
       </c>
       <c r="AE173" s="6">
-        <v>0.7155963302752294</v>
+        <v>0.71212121212121215</v>
       </c>
       <c r="AF173" s="9"/>
       <c r="AG173" s="5">
-        <v>-1156.5999999999999</v>
+        <v>-1589.7</v>
       </c>
       <c r="AH173" s="10">
         <v>0</v>
@@ -24216,7 +24216,7 @@
         <v>19954</v>
       </c>
       <c r="B179" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C179" s="4">
         <v>44</v>
@@ -24253,59 +24253,59 @@
         <v>52</v>
       </c>
       <c r="O179" s="5">
-        <v>10021.310000000001</v>
+        <v>15001.980000000001</v>
       </c>
       <c r="P179" s="5">
-        <v>11691.528333333335</v>
+        <v>15001.980000000001</v>
       </c>
       <c r="Q179" s="6">
-        <v>-0.24748959989358521</v>
+        <v>-0.034416574948347933</v>
       </c>
       <c r="R179" s="7">
-        <v>150.5</v>
+        <v>193</v>
       </c>
       <c r="S179" s="6">
-        <v>-0.22289156626506035</v>
+        <v>-0.16450216450216448</v>
       </c>
       <c r="T179" s="6">
-        <v>0.3656310103170145</v>
+        <v>0.36420253193245161</v>
       </c>
       <c r="U179" s="6">
-        <v>-0.010837734787168544</v>
+        <v>-0.0045214631668619746</v>
       </c>
       <c r="V179" s="6">
-        <v>0.15187086319054097</v>
+        <v>0.12734669023688874</v>
       </c>
       <c r="W179" s="6">
-        <v>0.080361250175875212</v>
+        <v>0.071120778723875122</v>
       </c>
       <c r="X179" s="8">
-        <v>25.603510526315791</v>
+        <v>26.389701123595504</v>
       </c>
       <c r="Y179" s="6">
-        <v>0.92982456140350878</v>
+        <v>0.8202247191011236</v>
       </c>
       <c r="Z179" s="6">
-        <v>0.070175438596491224</v>
+        <v>0.11235955056179775</v>
       </c>
       <c r="AA179" s="8">
-        <v>6.7216148437500003</v>
+        <v>7.7970489583333338</v>
       </c>
       <c r="AB179" s="8">
-        <v>3.9856719298245613</v>
+        <v>4.1503741573033714</v>
       </c>
       <c r="AC179" s="8">
-        <v>11.158771</v>
+        <v>11.667227</v>
       </c>
       <c r="AD179" s="8">
-        <v>18.122805263157897</v>
+        <v>18.628276404494382</v>
       </c>
       <c r="AE179" s="6">
-        <v>0.80701754385964908</v>
+        <v>0.7528089887640449</v>
       </c>
       <c r="AF179" s="9"/>
       <c r="AG179" s="5">
-        <v>-836.70000000000005</v>
+        <v>-1361.2</v>
       </c>
       <c r="AH179" s="10">
         <v>3</v>
@@ -24605,7 +24605,7 @@
         <v>19959</v>
       </c>
       <c r="B182" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C182" s="4">
         <v>44</v>
@@ -24642,55 +24642,55 @@
         <v>52</v>
       </c>
       <c r="O182" s="5">
-        <v>12641.25</v>
+        <v>18255.450000000001</v>
       </c>
       <c r="P182" s="5">
-        <v>14748.125</v>
+        <v>18255.450000000001</v>
       </c>
       <c r="Q182" s="6"/>
       <c r="R182" s="7">
-        <v>172.66666666666669</v>
+        <v>204</v>
       </c>
       <c r="S182" s="6"/>
       <c r="T182" s="6">
-        <v>0.40165424305349545</v>
+        <v>0.25767066821141082</v>
       </c>
       <c r="U182" s="6">
-        <v>0.067779823988925139</v>
+        <v>-0.062501663886674941</v>
       </c>
       <c r="V182" s="6">
-        <v>0.053125917136359141</v>
+        <v>0.04134981608232062</v>
       </c>
       <c r="W182" s="6">
-        <v>-0.001395589834866014</v>
+        <v>-0.0030900635152789988</v>
       </c>
       <c r="X182" s="8">
-        <v>25.431770312499999</v>
+        <v>25.083538271604937</v>
       </c>
       <c r="Y182" s="6">
-        <v>0.609375</v>
+        <v>0.69135802469135799</v>
       </c>
       <c r="Z182" s="6">
-        <v>0.0625</v>
+        <v>0.049382716049382713</v>
       </c>
       <c r="AA182" s="8">
-        <v>4.9819156028368798</v>
+        <v>5.649830612244898</v>
       </c>
       <c r="AB182" s="8">
-        <v>5.2502650793650796</v>
+        <v>4.6919835443037972</v>
       </c>
       <c r="AC182" s="8">
-        <v>10.145576</v>
+        <v>9.8600890000000003</v>
       </c>
       <c r="AD182" s="8">
-        <v>16.967968750000001</v>
+        <v>16.642181481481479</v>
       </c>
       <c r="AE182" s="6">
-        <v>0.8125</v>
+        <v>0.83950617283950613</v>
       </c>
       <c r="AF182" s="9"/>
       <c r="AG182" s="5">
-        <v>-1857.9000000000001</v>
+        <v>-2510.0999999999999</v>
       </c>
       <c r="AH182" s="10">
         <v>0</v>
@@ -24732,7 +24732,7 @@
         <v>19961</v>
       </c>
       <c r="B183" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C183" s="4">
         <v>44</v>
@@ -24769,55 +24769,55 @@
         <v>52</v>
       </c>
       <c r="O183" s="5">
-        <v>15856.34</v>
+        <v>20894.169999999998</v>
       </c>
       <c r="P183" s="5">
-        <v>18499.063333333335</v>
+        <v>20894.170000000002</v>
       </c>
       <c r="Q183" s="6"/>
       <c r="R183" s="7">
-        <v>208.83333333333331</v>
+        <v>229.99999999999997</v>
       </c>
       <c r="S183" s="6"/>
       <c r="T183" s="6">
-        <v>0.40059169392180033</v>
+        <v>0.37857962771433373</v>
       </c>
       <c r="U183" s="6">
-        <v>0.051127694032796975</v>
+        <v>0.029043369514079764</v>
       </c>
       <c r="V183" s="6">
-        <v>0.029425516859502256</v>
+        <v>0.027075447361632459</v>
       </c>
       <c r="W183" s="6">
-        <v>0.01183192338206673</v>
+        <v>0.010942238911619844</v>
       </c>
       <c r="X183" s="8">
-        <v>23.430069072164947</v>
+        <v>23.075806451612905</v>
       </c>
       <c r="Y183" s="6">
-        <v>0.5670103092783505</v>
+        <v>0.59677419354838712</v>
       </c>
       <c r="Z183" s="6">
-        <v>0.051546391752577317</v>
+        <v>0.040322580645161289</v>
       </c>
       <c r="AA183" s="8">
-        <v>6.1321833333333338</v>
+        <v>6.0183031250000001</v>
       </c>
       <c r="AB183" s="8">
-        <v>3.3527173913043478</v>
+        <v>3.4462965811965813</v>
       </c>
       <c r="AC183" s="8">
-        <v>9.9004440000000002</v>
+        <v>9.7113219999999991</v>
       </c>
       <c r="AD183" s="8">
-        <v>16.492095876288662</v>
+        <v>16.221774193548388</v>
       </c>
       <c r="AE183" s="6">
-        <v>0.81443298969072164</v>
+        <v>0.84677419354838712</v>
       </c>
       <c r="AF183" s="9"/>
       <c r="AG183" s="5">
-        <v>-1427.9000000000001</v>
+        <v>-2004.0999999999999</v>
       </c>
       <c r="AH183" s="10">
         <v>2</v>

--- a/franquias/pwr_reports/Keys Summary - Franquias (Stores)(2026-08-03 - 2026-08-09).xlsx
+++ b/franquias/pwr_reports/Keys Summary - Franquias (Stores)(2026-08-03 - 2026-08-09).xlsx
@@ -689,129 +689,132 @@
     <t>VERVLOET,HUGO LEONARDO LOUZADA</t>
   </si>
   <si>
+    <t>DURANTE,RAFAEL BARROS</t>
+  </si>
+  <si>
+    <t>Guarujá</t>
+  </si>
+  <si>
+    <t>MANAUS</t>
+  </si>
+  <si>
+    <t>BRASILIA</t>
+  </si>
+  <si>
+    <t>Risuenho,Igor and Vinicius Costa</t>
+  </si>
+  <si>
+    <t>Canoas</t>
+  </si>
+  <si>
+    <t>Guarulhos</t>
+  </si>
+  <si>
+    <t>RYNALDO CALSAVARA,ANDRE</t>
+  </si>
+  <si>
+    <t>PETROLINA</t>
+  </si>
+  <si>
+    <t>Coelho,Caio Bezerra de Souza</t>
+  </si>
+  <si>
+    <t>TAGUATINGA</t>
+  </si>
+  <si>
+    <t>MONTES CLAROS</t>
+  </si>
+  <si>
+    <t>MARTINS,RODRIGO LUIS and WILSON ATHAYDE RIBEIRO</t>
+  </si>
+  <si>
+    <t>FORTALEZA</t>
+  </si>
+  <si>
+    <t>VARGINHA</t>
+  </si>
+  <si>
+    <t>Poloni,Gabriel Godoy</t>
+  </si>
+  <si>
+    <t>ARMACAO DOS BUZIOS</t>
+  </si>
+  <si>
+    <t>DE ALMEIDA,MATHEUS OLIVEIRA</t>
+  </si>
+  <si>
+    <t>LUIS EDUARDO MAGALHAES</t>
+  </si>
+  <si>
+    <t>de Araujo Chaves,Jaqueline</t>
+  </si>
+  <si>
+    <t>GARANHUNS</t>
+  </si>
+  <si>
+    <t>UBERABA</t>
+  </si>
+  <si>
+    <t>SILVA,FERNANDO SEIXLACK</t>
+  </si>
+  <si>
+    <t>PARAUAPEBAS</t>
+  </si>
+  <si>
+    <t>Duarte,Patricia</t>
+  </si>
+  <si>
+    <t>VIEIRA,TYCIANA</t>
+  </si>
+  <si>
+    <t>Ponta Grossa</t>
+  </si>
+  <si>
+    <t>MAGAGNIN,ALEXANDRE</t>
+  </si>
+  <si>
+    <t>GUARAPUAVA</t>
+  </si>
+  <si>
+    <t>Abdallah,Bruno</t>
+  </si>
+  <si>
+    <t>Americana</t>
+  </si>
+  <si>
+    <t>Reis Filho,Abnadar</t>
+  </si>
+  <si>
+    <t>BOTUCATU</t>
+  </si>
+  <si>
+    <t>DE ALMEIDA,DIEGO EMANUEL</t>
+  </si>
+  <si>
+    <t>Pedro,Joao and Marcilio Menezes</t>
+  </si>
+  <si>
+    <t>Passo Fundo</t>
+  </si>
+  <si>
+    <t>CAMARA,DAIANE</t>
+  </si>
+  <si>
+    <t>NATAL, RN</t>
+  </si>
+  <si>
+    <t>ITUIUTABA</t>
+  </si>
+  <si>
+    <t>Mamede Marquez,Carlos</t>
+  </si>
+  <si>
+    <t>Cachoeiro de Itapemirim</t>
+  </si>
+  <si>
     <t>DURANTE,DANIEL BARROS and DANIELA PIMENTEL MOREIRA</t>
   </si>
   <si>
-    <t>Guarujá</t>
-  </si>
-  <si>
-    <t>MANAUS</t>
-  </si>
-  <si>
-    <t>BRASILIA</t>
-  </si>
-  <si>
-    <t>Risuenho,Igor and Vinicius Costa</t>
-  </si>
-  <si>
-    <t>Canoas</t>
-  </si>
-  <si>
-    <t>Guarulhos</t>
-  </si>
-  <si>
-    <t>RYNALDO CALSAVARA,ANDRE</t>
-  </si>
-  <si>
-    <t>PETROLINA</t>
-  </si>
-  <si>
-    <t>Coelho,Caio Bezerra de Souza</t>
-  </si>
-  <si>
-    <t>TAGUATINGA</t>
-  </si>
-  <si>
-    <t>MONTES CLAROS</t>
-  </si>
-  <si>
-    <t>MARTINS,RODRIGO LUIS and WILSON ATHAYDE RIBEIRO</t>
-  </si>
-  <si>
-    <t>FORTALEZA</t>
-  </si>
-  <si>
-    <t>VARGINHA</t>
-  </si>
-  <si>
-    <t>Poloni,Gabriel Godoy</t>
-  </si>
-  <si>
-    <t>ARMACAO DOS BUZIOS</t>
-  </si>
-  <si>
-    <t>DE ALMEIDA,MATHEUS OLIVEIRA</t>
-  </si>
-  <si>
-    <t>LUIS EDUARDO MAGALHAES</t>
-  </si>
-  <si>
-    <t>de Araujo Chaves,Jaqueline</t>
-  </si>
-  <si>
-    <t>GARANHUNS</t>
-  </si>
-  <si>
-    <t>UBERABA</t>
-  </si>
-  <si>
-    <t>SILVA,FERNANDO SEIXLACK</t>
-  </si>
-  <si>
-    <t>PARAUAPEBAS</t>
-  </si>
-  <si>
-    <t>Duarte,Patricia</t>
-  </si>
-  <si>
-    <t>VIEIRA,TYCIANA</t>
-  </si>
-  <si>
-    <t>Ponta Grossa</t>
-  </si>
-  <si>
-    <t>MAGAGNIN,ALEXANDRE</t>
-  </si>
-  <si>
-    <t>GUARAPUAVA</t>
-  </si>
-  <si>
-    <t>Abdallah,Bruno</t>
-  </si>
-  <si>
-    <t>Americana</t>
-  </si>
-  <si>
-    <t>Reis Filho,Abnadar</t>
-  </si>
-  <si>
-    <t>BOTUCATU</t>
-  </si>
-  <si>
-    <t>DE ALMEIDA,DIEGO EMANUEL</t>
-  </si>
-  <si>
-    <t>Pedro,Joao and Marcilio Menezes</t>
-  </si>
-  <si>
-    <t>Passo Fundo</t>
-  </si>
-  <si>
-    <t>CAMARA,DAIANE</t>
-  </si>
-  <si>
-    <t>NATAL, RN</t>
-  </si>
-  <si>
-    <t>ITUIUTABA</t>
-  </si>
-  <si>
-    <t>Mamede Marquez,Carlos</t>
-  </si>
-  <si>
-    <t>Cachoeiro de Itapemirim</t>
-  </si>
-  <si>
     <t>AP</t>
   </si>
   <si>
@@ -885,33 +888,33 @@
   </si>
   <si>
     <t>187
-165</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>R$ 7.184.767,98</t>
-  </si>
-  <si>
-    <t>R$ 42.334,49
-R$ 42.104,13</t>
-  </si>
-  <si>
-    <t>10.2%
-9.8%</t>
-  </si>
-  <si>
-    <t>457.0</t>
-  </si>
-  <si>
-    <t>(4.4%)</t>
-  </si>
-  <si>
-    <t>17.0%</t>
-  </si>
-  <si>
-    <t>(25.7%)</t>
+177</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>R$ 7.091.496,65</t>
+  </si>
+  <si>
+    <t>R$ 37.922,44
+R$ 38.530,47</t>
+  </si>
+  <si>
+    <t>(1.3%)
+(0.9%)</t>
+  </si>
+  <si>
+    <t>456.8</t>
+  </si>
+  <si>
+    <t>(4.5%)</t>
+  </si>
+  <si>
+    <t>17.1%</t>
+  </si>
+  <si>
+    <t>(25.2%)</t>
   </si>
   <si>
     <t>3.2%</t>
@@ -920,34 +923,34 @@
     <t>0.6%</t>
   </si>
   <si>
-    <t>28.1</t>
-  </si>
-  <si>
-    <t>64.5%</t>
-  </si>
-  <si>
-    <t>12.1%</t>
-  </si>
-  <si>
-    <t>5.7</t>
-  </si>
-  <si>
-    <t>7.3</t>
-  </si>
-  <si>
-    <t>13.0</t>
-  </si>
-  <si>
-    <t>19.7</t>
-  </si>
-  <si>
-    <t>67.9%</t>
-  </si>
-  <si>
-    <t>-R$ 192.001,94</t>
-  </si>
-  <si>
-    <t>2.72</t>
+    <t>28.3</t>
+  </si>
+  <si>
+    <t>64.0%</t>
+  </si>
+  <si>
+    <t>12.5%</t>
+  </si>
+  <si>
+    <t>5.8</t>
+  </si>
+  <si>
+    <t>7.4</t>
+  </si>
+  <si>
+    <t>13.2</t>
+  </si>
+  <si>
+    <t>19.9</t>
+  </si>
+  <si>
+    <t>67.2%</t>
+  </si>
+  <si>
+    <t>-R$ 196.098,30</t>
+  </si>
+  <si>
+    <t>2.74</t>
   </si>
   <si>
     <t>3.14</t>
@@ -1369,7 +1372,7 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="5.43" customWidth="1"/>
-    <col min="2" max="2" width="3.57" customWidth="1"/>
+    <col min="2" max="2" width="3.14" customWidth="1"/>
     <col min="3" max="3" width="17.86" customWidth="1"/>
     <col min="4" max="4" width="4.43" customWidth="1"/>
     <col min="5" max="5" width="26.57" customWidth="1"/>
@@ -1594,13 +1597,13 @@
         <v>52</v>
       </c>
       <c r="O2" s="5">
-        <v>55740.789999999994</v>
+        <v>49515.610000000001</v>
       </c>
       <c r="P2" s="5">
-        <v>55740.789999999994</v>
+        <v>49515.610000000001</v>
       </c>
       <c r="Q2" s="6">
-        <v>0.04414884998206392</v>
+        <v>-0.072462603460403341</v>
       </c>
       <c r="R2" s="7">
         <v>588</v>
@@ -1723,13 +1726,13 @@
         <v>52</v>
       </c>
       <c r="O3" s="5">
-        <v>67474.380000000005</v>
+        <v>63405.629999999997</v>
       </c>
       <c r="P3" s="5">
-        <v>67474.380000000005</v>
+        <v>63405.629999999997</v>
       </c>
       <c r="Q3" s="6">
-        <v>0.11512768267314466</v>
+        <v>0.047884741591265101</v>
       </c>
       <c r="R3" s="7">
         <v>661</v>
@@ -1854,13 +1857,13 @@
         <v>52</v>
       </c>
       <c r="O4" s="5">
-        <v>57032.650000000001</v>
+        <v>51692.660000000003</v>
       </c>
       <c r="P4" s="5">
-        <v>57032.650000000001</v>
+        <v>51692.659999999996</v>
       </c>
       <c r="Q4" s="6">
-        <v>0.068551824510087345</v>
+        <v>-0.031497113376642849</v>
       </c>
       <c r="R4" s="7">
         <v>596</v>
@@ -1985,13 +1988,13 @@
         <v>52</v>
       </c>
       <c r="O5" s="5">
-        <v>26095.080000000002</v>
+        <v>23112.32</v>
       </c>
       <c r="P5" s="5">
-        <v>26095.079999999998</v>
+        <v>23112.32</v>
       </c>
       <c r="Q5" s="6">
-        <v>0.57108513816415707</v>
+        <v>0.39150454646984056</v>
       </c>
       <c r="R5" s="7">
         <v>276</v>
@@ -2116,13 +2119,13 @@
         <v>52</v>
       </c>
       <c r="O6" s="5">
-        <v>73769.509999999995</v>
+        <v>67389.539999999994</v>
       </c>
       <c r="P6" s="5">
-        <v>73769.509999999995</v>
+        <v>67389.539999999994</v>
       </c>
       <c r="Q6" s="6">
-        <v>0.20478864613487624</v>
+        <v>0.10059227261035186</v>
       </c>
       <c r="R6" s="7">
         <v>743</v>
@@ -2247,13 +2250,13 @@
         <v>52</v>
       </c>
       <c r="O7" s="5">
-        <v>67124.699999999997</v>
+        <v>59184.059999999998</v>
       </c>
       <c r="P7" s="5">
-        <v>67124.699999999997</v>
+        <v>59184.059999999998</v>
       </c>
       <c r="Q7" s="6">
-        <v>0.1636994869817634</v>
+        <v>0.026037513158314374</v>
       </c>
       <c r="R7" s="7">
         <v>673</v>
@@ -2378,13 +2381,13 @@
         <v>52</v>
       </c>
       <c r="O8" s="5">
-        <v>42701.629999999997</v>
+        <v>38382.400000000001</v>
       </c>
       <c r="P8" s="5">
-        <v>42701.629999999997</v>
+        <v>38382.400000000001</v>
       </c>
       <c r="Q8" s="6">
-        <v>0.080408414213280155</v>
+        <v>-0.028873888006153203</v>
       </c>
       <c r="R8" s="7">
         <v>501</v>
@@ -2509,13 +2512,13 @@
         <v>52</v>
       </c>
       <c r="O9" s="5">
-        <v>85751.160000000003</v>
+        <v>80691.479999999996</v>
       </c>
       <c r="P9" s="5">
-        <v>85751.160000000003</v>
+        <v>80691.479999999996</v>
       </c>
       <c r="Q9" s="6">
-        <v>0.16554703173507179</v>
+        <v>0.096774842466386346</v>
       </c>
       <c r="R9" s="7">
         <v>833</v>
@@ -2640,13 +2643,13 @@
         <v>52</v>
       </c>
       <c r="O10" s="5">
-        <v>56527.809999999998</v>
+        <v>50295.730000000003</v>
       </c>
       <c r="P10" s="5">
-        <v>56527.809999999998</v>
+        <v>50295.730000000003</v>
       </c>
       <c r="Q10" s="6">
-        <v>0.085291721128547326</v>
+        <v>-0.03435955900084009</v>
       </c>
       <c r="R10" s="7">
         <v>581</v>
@@ -2771,13 +2774,13 @@
         <v>52</v>
       </c>
       <c r="O11" s="5">
-        <v>105959.95000000001</v>
+        <v>99277.199999999997</v>
       </c>
       <c r="P11" s="5">
-        <v>105959.95000000003</v>
+        <v>99277.199999999997</v>
       </c>
       <c r="Q11" s="6">
-        <v>0.091234609578605852</v>
+        <v>0.022411926223607548</v>
       </c>
       <c r="R11" s="7">
         <v>1130</v>
@@ -2865,7 +2868,7 @@
         <v>19536</v>
       </c>
       <c r="B12" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c t="s" r="C12" s="4">
         <v>44</v>
@@ -2901,25 +2904,61 @@
       <c t="s" r="N12" s="4">
         <v>52</v>
       </c>
-      <c r="O12" s="5"/>
-      <c r="P12" s="5"/>
-      <c r="Q12" s="6"/>
-      <c r="R12" s="7"/>
-      <c r="S12" s="6"/>
-      <c r="T12" s="6"/>
-      <c r="U12" s="6"/>
-      <c r="V12" s="6"/>
-      <c r="W12" s="6"/>
-      <c r="X12" s="8"/>
-      <c r="Y12" s="6"/>
-      <c r="Z12" s="6"/>
-      <c r="AA12" s="8"/>
-      <c r="AB12" s="8"/>
-      <c r="AC12" s="8"/>
-      <c r="AD12" s="8"/>
-      <c r="AE12" s="6"/>
+      <c r="O12" s="5">
+        <v>44517.360000000001</v>
+      </c>
+      <c r="P12" s="5">
+        <v>44517.360000000001</v>
+      </c>
+      <c r="Q12" s="6">
+        <v>-0.078368574231131194</v>
+      </c>
+      <c r="R12" s="7">
+        <v>583</v>
+      </c>
+      <c r="S12" s="6">
+        <v>-0.09048361934477378</v>
+      </c>
+      <c r="T12" s="6">
+        <v>0.29391450764534821</v>
+      </c>
+      <c r="U12" s="6">
+        <v>-0.04881379473145895</v>
+      </c>
+      <c r="V12" s="6">
+        <v>0.028833344956058087</v>
+      </c>
+      <c r="W12" s="6">
+        <v>0.0037156348091789068</v>
+      </c>
+      <c r="X12" s="8">
+        <v>34.399055102040819</v>
+      </c>
+      <c r="Y12" s="6">
+        <v>0.5374149659863946</v>
+      </c>
+      <c r="Z12" s="6">
+        <v>0.26530612244897961</v>
+      </c>
+      <c r="AA12" s="8">
+        <v>5.2619891651865007</v>
+      </c>
+      <c r="AB12" s="8">
+        <v>11.559377448747153</v>
+      </c>
+      <c r="AC12" s="8">
+        <v>17.055966999999999</v>
+      </c>
+      <c r="AD12" s="8">
+        <v>23.919123129251702</v>
+      </c>
+      <c r="AE12" s="6">
+        <v>0.48072562358276644</v>
+      </c>
       <c r="AF12" s="9"/>
-      <c r="AG12" s="5"/>
+      <c r="AG12" s="5">
+        <v>-2317.3800000000001</v>
+      </c>
       <c r="AH12" s="10">
         <v>2</v>
       </c>
@@ -2997,13 +3036,13 @@
         <v>52</v>
       </c>
       <c r="O13" s="5">
-        <v>70150.400000000009</v>
+        <v>61919.010000000002</v>
       </c>
       <c r="P13" s="5">
-        <v>70150.400000000009</v>
+        <v>61919.010000000002</v>
       </c>
       <c r="Q13" s="6">
-        <v>0.34115038884536331</v>
+        <v>0.18378090985111872</v>
       </c>
       <c r="R13" s="7">
         <v>698</v>
@@ -3128,13 +3167,13 @@
         <v>52</v>
       </c>
       <c r="O14" s="5">
-        <v>84502.369999999995</v>
+        <v>81451.949999999997</v>
       </c>
       <c r="P14" s="5">
-        <v>84502.369999999995</v>
+        <v>81451.949999999997</v>
       </c>
       <c r="Q14" s="6">
-        <v>-0.180924052658612</v>
+        <v>-0.21049157427119058</v>
       </c>
       <c r="R14" s="7">
         <v>926</v>
@@ -3259,13 +3298,13 @@
         <v>52</v>
       </c>
       <c r="O15" s="5">
-        <v>37865.790000000001</v>
+        <v>33703.839999999997</v>
       </c>
       <c r="P15" s="5">
-        <v>37865.790000000001</v>
+        <v>33703.839999999997</v>
       </c>
       <c r="Q15" s="6">
-        <v>-0.32997860718437633</v>
+        <v>-0.40362279989312444</v>
       </c>
       <c r="R15" s="7">
         <v>386</v>
@@ -3390,13 +3429,13 @@
         <v>52</v>
       </c>
       <c r="O16" s="5">
-        <v>45140.139999999999</v>
+        <v>40524.370000000003</v>
       </c>
       <c r="P16" s="5">
-        <v>45140.139999999999</v>
+        <v>40524.370000000003</v>
       </c>
       <c r="Q16" s="6">
-        <v>0.17445401326915588</v>
+        <v>0.054361129179133716</v>
       </c>
       <c r="R16" s="7">
         <v>493</v>
@@ -3521,13 +3560,13 @@
         <v>52</v>
       </c>
       <c r="O17" s="5">
-        <v>36473.979999999996</v>
+        <v>32871.540000000001</v>
       </c>
       <c r="P17" s="5">
-        <v>36473.979999999996</v>
+        <v>32871.540000000001</v>
       </c>
       <c r="Q17" s="6">
-        <v>-0.053359570951613811</v>
+        <v>-0.14685678039300365</v>
       </c>
       <c r="R17" s="7">
         <v>426</v>
@@ -3652,10 +3691,10 @@
         <v>52</v>
       </c>
       <c r="O18" s="5">
-        <v>38828.729999999996</v>
+        <v>32929.989999999998</v>
       </c>
       <c r="P18" s="5">
-        <v>38828.729999999996</v>
+        <v>32929.989999999998</v>
       </c>
       <c r="Q18" s="6"/>
       <c r="R18" s="7">
@@ -3781,13 +3820,13 @@
         <v>52</v>
       </c>
       <c r="O19" s="5">
-        <v>61274.810000000005</v>
+        <v>52867.900000000001</v>
       </c>
       <c r="P19" s="5">
-        <v>61274.810000000005</v>
+        <v>52867.900000000001</v>
       </c>
       <c r="Q19" s="6">
-        <v>0.094690924604458493</v>
+        <v>-0.055500778657721628</v>
       </c>
       <c r="R19" s="7">
         <v>556</v>
@@ -3912,13 +3951,13 @@
         <v>52</v>
       </c>
       <c r="O20" s="5">
-        <v>92535.699999999997</v>
+        <v>76332.029999999999</v>
       </c>
       <c r="P20" s="5">
-        <v>92535.699999999997</v>
+        <v>76332.029999999999</v>
       </c>
       <c r="Q20" s="6">
-        <v>0.23250764093015874</v>
+        <v>0.016686643346407015</v>
       </c>
       <c r="R20" s="7">
         <v>960</v>
@@ -4041,13 +4080,13 @@
         <v>52</v>
       </c>
       <c r="O21" s="5">
-        <v>59362</v>
+        <v>50201.839999999997</v>
       </c>
       <c r="P21" s="5">
-        <v>59362</v>
+        <v>50201.840000000004</v>
       </c>
       <c r="Q21" s="6">
-        <v>0.3768836994616509</v>
+        <v>0.16441654895357116</v>
       </c>
       <c r="R21" s="7">
         <v>544</v>
@@ -4172,13 +4211,13 @@
         <v>52</v>
       </c>
       <c r="O22" s="5">
-        <v>58474.400000000001</v>
+        <v>51152.139999999999</v>
       </c>
       <c r="P22" s="5">
-        <v>58474.400000000001</v>
+        <v>51152.139999999999</v>
       </c>
       <c r="Q22" s="6">
-        <v>-0.066120019861223733</v>
+        <v>-0.18306199828889391</v>
       </c>
       <c r="R22" s="7">
         <v>622</v>
@@ -4303,13 +4342,13 @@
         <v>52</v>
       </c>
       <c r="O23" s="5">
-        <v>31342.619999999999</v>
+        <v>28427.630000000001</v>
       </c>
       <c r="P23" s="5">
-        <v>31342.619999999999</v>
+        <v>28427.630000000001</v>
       </c>
       <c r="Q23" s="6">
-        <v>0.16730942771238033</v>
+        <v>0.058744945589082498</v>
       </c>
       <c r="R23" s="7">
         <v>355</v>
@@ -4434,13 +4473,13 @@
         <v>52</v>
       </c>
       <c r="O24" s="5">
-        <v>53742.440000000002</v>
+        <v>47774.139999999999</v>
       </c>
       <c r="P24" s="5">
-        <v>53742.440000000002</v>
+        <v>47774.139999999999</v>
       </c>
       <c r="Q24" s="6">
-        <v>0.10876343417175893</v>
+        <v>-0.014368913450852006</v>
       </c>
       <c r="R24" s="7">
         <v>591</v>
@@ -4565,13 +4604,13 @@
         <v>52</v>
       </c>
       <c r="O25" s="5">
-        <v>93185.449999999997</v>
+        <v>83823.910000000003</v>
       </c>
       <c r="P25" s="5">
-        <v>93185.449999999997</v>
+        <v>83823.910000000003</v>
       </c>
       <c r="Q25" s="6">
-        <v>0.28288473311899942</v>
+        <v>0.15400434734543889</v>
       </c>
       <c r="R25" s="7">
         <v>1179</v>
@@ -4696,13 +4735,13 @@
         <v>52</v>
       </c>
       <c r="O26" s="5">
-        <v>37562.809999999998</v>
+        <v>33645.510000000002</v>
       </c>
       <c r="P26" s="5">
-        <v>37562.809999999998</v>
+        <v>33645.510000000002</v>
       </c>
       <c r="Q26" s="6">
-        <v>-0.031202189174829753</v>
+        <v>-0.13223487720709981</v>
       </c>
       <c r="R26" s="7">
         <v>425</v>
@@ -4790,7 +4829,7 @@
         <v>19579</v>
       </c>
       <c r="B27" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c t="s" r="C27" s="4">
         <v>44</v>
@@ -4827,59 +4866,59 @@
         <v>52</v>
       </c>
       <c r="O27" s="5">
-        <v>10118.040000000001</v>
+        <v>36955.860000000001</v>
       </c>
       <c r="P27" s="5">
-        <v>23608.759999999998</v>
+        <v>36955.860000000001</v>
       </c>
       <c r="Q27" s="6">
-        <v>-0.44126501782673566</v>
+        <v>-0.12538685732339816</v>
       </c>
       <c r="R27" s="7">
-        <v>268.33333333333337</v>
+        <v>420</v>
       </c>
       <c r="S27" s="6">
-        <v>-0.1085271317829456</v>
+        <v>-0.045454545454545414</v>
       </c>
       <c r="T27" s="6">
-        <v>0.3251242434305458</v>
+        <v>0.32265046257566499</v>
       </c>
       <c r="U27" s="6">
-        <v>0.011089114097196691</v>
+        <v>0.031433978271485905</v>
       </c>
       <c r="V27" s="6">
-        <v>0.052954870706184196</v>
+        <v>0.041399282895129133</v>
       </c>
       <c r="W27" s="6">
-        <v>-0.00098838312558558773</v>
+        <v>0.0047698720346963826</v>
       </c>
       <c r="X27" s="8">
-        <v>24.190049253731345</v>
+        <v>26.640779787234042</v>
       </c>
       <c r="Y27" s="6">
-        <v>0.91044776119402981</v>
+        <v>0.76595744680851063</v>
       </c>
       <c r="Z27" s="6">
-        <v>0.029850746268656716</v>
+        <v>0.056737588652482268</v>
       </c>
       <c r="AA27" s="8">
-        <v>5.0342342342342334</v>
+        <v>5.9843723192019951</v>
       </c>
       <c r="AB27" s="8">
-        <v>4.798010447761194</v>
+        <v>6.5442264285714282</v>
       </c>
       <c r="AC27" s="8">
-        <v>10.192705</v>
+        <v>13.029999</v>
       </c>
       <c r="AD27" s="8">
-        <v>17.01044776119403</v>
+        <v>19.854905319148937</v>
       </c>
       <c r="AE27" s="6">
-        <v>0.91044776119402981</v>
+        <v>0.74113475177304966</v>
       </c>
       <c r="AF27" s="9"/>
       <c r="AG27" s="5">
-        <v>-122.8</v>
+        <v>-439.89999999999998</v>
       </c>
       <c r="AH27" s="10">
         <v>3</v>
@@ -4958,13 +4997,13 @@
         <v>52</v>
       </c>
       <c r="O28" s="5">
-        <v>44431.940000000002</v>
+        <v>42245.879999999997</v>
       </c>
       <c r="P28" s="5">
-        <v>44431.940000000002</v>
+        <v>42245.879999999997</v>
       </c>
       <c r="Q28" s="6">
-        <v>-0.099019935468067422</v>
+        <v>-0.14334832805841302</v>
       </c>
       <c r="R28" s="7">
         <v>435</v>
@@ -5089,13 +5128,13 @@
         <v>52</v>
       </c>
       <c r="O29" s="5">
-        <v>54526.700000000004</v>
+        <v>51843.980000000003</v>
       </c>
       <c r="P29" s="5">
-        <v>54526.700000000004</v>
+        <v>51843.980000000003</v>
       </c>
       <c r="Q29" s="6">
-        <v>-0.022647521850159613</v>
+        <v>-0.070733377773627315</v>
       </c>
       <c r="R29" s="7">
         <v>539</v>
@@ -5220,13 +5259,13 @@
         <v>52</v>
       </c>
       <c r="O30" s="5">
-        <v>81625.360000000001</v>
+        <v>73127.520000000004</v>
       </c>
       <c r="P30" s="5">
-        <v>81625.360000000001</v>
+        <v>73127.520000000004</v>
       </c>
       <c r="Q30" s="6">
-        <v>0.22651189369445701</v>
+        <v>0.098822388487833646</v>
       </c>
       <c r="R30" s="7">
         <v>809</v>
@@ -5349,13 +5388,13 @@
         <v>52</v>
       </c>
       <c r="O31" s="5">
-        <v>48944.869999999995</v>
+        <v>43431.970000000001</v>
       </c>
       <c r="P31" s="5">
-        <v>48944.869999999995</v>
+        <v>43431.970000000008</v>
       </c>
       <c r="Q31" s="6">
-        <v>0.27097774530104402</v>
+        <v>0.1278213080264099</v>
       </c>
       <c r="R31" s="7">
         <v>537</v>
@@ -5480,13 +5519,13 @@
         <v>52</v>
       </c>
       <c r="O32" s="5">
-        <v>65975.369999999995</v>
+        <v>58329.919999999998</v>
       </c>
       <c r="P32" s="5">
-        <v>65975.369999999995</v>
+        <v>58329.919999999998</v>
       </c>
       <c r="Q32" s="6">
-        <v>0.22791158118390298</v>
+        <v>0.085617015827733178</v>
       </c>
       <c r="R32" s="7">
         <v>737</v>
@@ -5609,13 +5648,13 @@
         <v>52</v>
       </c>
       <c r="O33" s="5">
-        <v>53705.309999999998</v>
+        <v>47911.220000000001</v>
       </c>
       <c r="P33" s="5">
-        <v>53705.309999999998</v>
+        <v>47911.220000000008</v>
       </c>
       <c r="Q33" s="6">
-        <v>0.17302710669690757</v>
+        <v>0.046473054059626762</v>
       </c>
       <c r="R33" s="7">
         <v>617</v>
@@ -5738,13 +5777,13 @@
         <v>52</v>
       </c>
       <c r="O34" s="5">
-        <v>45022.970000000001</v>
+        <v>42897.879999999997</v>
       </c>
       <c r="P34" s="5">
-        <v>45022.970000000008</v>
+        <v>42897.879999999997</v>
       </c>
       <c r="Q34" s="6">
-        <v>0.068368714285748089</v>
+        <v>0.01794157296118648</v>
       </c>
       <c r="R34" s="7">
         <v>534</v>
@@ -5869,13 +5908,13 @@
         <v>52</v>
       </c>
       <c r="O35" s="5">
-        <v>51976.509999999995</v>
+        <v>46250.830000000002</v>
       </c>
       <c r="P35" s="5">
-        <v>51976.509999999995</v>
+        <v>46250.830000000002</v>
       </c>
       <c r="Q35" s="6">
-        <v>0.097143393900502861</v>
+        <v>-0.023716817521699518</v>
       </c>
       <c r="R35" s="7">
         <v>577</v>
@@ -5963,7 +6002,7 @@
         <v>19602</v>
       </c>
       <c r="B36" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>44</v>
@@ -5999,25 +6038,61 @@
       <c t="s" r="N36" s="4">
         <v>52</v>
       </c>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="7"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="8"/>
-      <c r="Y36" s="6"/>
-      <c r="Z36" s="6"/>
-      <c r="AA36" s="8"/>
-      <c r="AB36" s="8"/>
-      <c r="AC36" s="8"/>
-      <c r="AD36" s="8"/>
-      <c r="AE36" s="6"/>
+      <c r="O36" s="5">
+        <v>6079.0600000000004</v>
+      </c>
+      <c r="P36" s="5">
+        <v>6079.0600000000004</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>0.90583469970624297</v>
+      </c>
+      <c r="R36" s="7">
+        <v>70</v>
+      </c>
+      <c r="S36" s="6">
+        <v>0.89189189189189189</v>
+      </c>
+      <c r="T36" s="6">
+        <v>0</v>
+      </c>
+      <c r="U36" s="6">
+        <v>-0.32637450776920318</v>
+      </c>
+      <c r="V36" s="6">
+        <v>0.037513990909873618</v>
+      </c>
+      <c r="W36" s="6">
+        <v>-0.1019842546564618</v>
+      </c>
+      <c r="X36" s="8">
+        <v>33.004288571428575</v>
+      </c>
+      <c r="Y36" s="6">
+        <v>0.59999999999999998</v>
+      </c>
+      <c r="Z36" s="6">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="AA36" s="8">
+        <v>6.2978571428571435</v>
+      </c>
+      <c r="AB36" s="8">
+        <v>14.746665714285713</v>
+      </c>
+      <c r="AC36" s="8">
+        <v>21.433807999999999</v>
+      </c>
+      <c r="AD36" s="8">
+        <v>28.357617142857144</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>0.42857142857142855</v>
+      </c>
       <c r="AF36" s="9"/>
-      <c r="AG36" s="5"/>
+      <c r="AG36" s="5">
+        <v>0</v>
+      </c>
       <c r="AH36" s="10">
         <v>2</v>
       </c>
@@ -6095,13 +6170,13 @@
         <v>52</v>
       </c>
       <c r="O37" s="5">
-        <v>14335.290000000001</v>
+        <v>12731.75</v>
       </c>
       <c r="P37" s="5">
-        <v>14335.289999999999</v>
+        <v>12731.75</v>
       </c>
       <c r="Q37" s="6">
-        <v>-0.67209054006636282</v>
+        <v>-0.70877036554474415</v>
       </c>
       <c r="R37" s="7">
         <v>158</v>
@@ -6224,13 +6299,13 @@
         <v>52</v>
       </c>
       <c r="O38" s="5">
-        <v>36651.300000000003</v>
+        <v>34664.800000000003</v>
       </c>
       <c r="P38" s="5">
-        <v>36651.300000000003</v>
+        <v>34664.800000000003</v>
       </c>
       <c r="Q38" s="6">
-        <v>0.42438641824797774</v>
+        <v>0.34718469225600423</v>
       </c>
       <c r="R38" s="7">
         <v>422</v>
@@ -6355,13 +6430,13 @@
         <v>52</v>
       </c>
       <c r="O39" s="5">
-        <v>36712.830000000002</v>
+        <v>32971.400000000001</v>
       </c>
       <c r="P39" s="5">
-        <v>36712.830000000002</v>
+        <v>32971.400000000001</v>
       </c>
       <c r="Q39" s="6">
-        <v>-0.086057792244163767</v>
+        <v>-0.17919827731066296</v>
       </c>
       <c r="R39" s="7">
         <v>419</v>
@@ -6486,13 +6561,13 @@
         <v>52</v>
       </c>
       <c r="O40" s="5">
-        <v>45697.510000000002</v>
+        <v>40607.610000000001</v>
       </c>
       <c r="P40" s="5">
-        <v>45697.510000000002</v>
+        <v>40607.610000000001</v>
       </c>
       <c r="Q40" s="6">
-        <v>0.24656079142646781</v>
+        <v>0.10771581338977421</v>
       </c>
       <c r="R40" s="7">
         <v>551</v>
@@ -6615,13 +6690,13 @@
         <v>52</v>
       </c>
       <c r="O41" s="5">
-        <v>60922.710000000006</v>
+        <v>55689.099999999999</v>
       </c>
       <c r="P41" s="5">
-        <v>60922.710000000006</v>
+        <v>55689.099999999999</v>
       </c>
       <c r="Q41" s="6">
-        <v>-0.044080640104838809</v>
+        <v>-0.12619959248139789</v>
       </c>
       <c r="R41" s="7">
         <v>668</v>
@@ -6746,13 +6821,13 @@
         <v>52</v>
       </c>
       <c r="O42" s="5">
-        <v>70852.279999999999</v>
+        <v>61599.889999999999</v>
       </c>
       <c r="P42" s="5">
-        <v>70852.279999999999</v>
+        <v>61599.889999999999</v>
       </c>
       <c r="Q42" s="6">
-        <v>0.15328401093574318</v>
+        <v>0.0026800578951102771</v>
       </c>
       <c r="R42" s="7">
         <v>737</v>
@@ -6840,7 +6915,7 @@
         <v>19618</v>
       </c>
       <c r="B43" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c t="s" r="C43" s="4">
         <v>44</v>
@@ -6876,25 +6951,61 @@
       <c t="s" r="N43" s="4">
         <v>52</v>
       </c>
-      <c r="O43" s="5"/>
-      <c r="P43" s="5"/>
-      <c r="Q43" s="6"/>
-      <c r="R43" s="7"/>
-      <c r="S43" s="6"/>
-      <c r="T43" s="6"/>
-      <c r="U43" s="6"/>
-      <c r="V43" s="6"/>
-      <c r="W43" s="6"/>
-      <c r="X43" s="8"/>
-      <c r="Y43" s="6"/>
-      <c r="Z43" s="6"/>
-      <c r="AA43" s="8"/>
-      <c r="AB43" s="8"/>
-      <c r="AC43" s="8"/>
-      <c r="AD43" s="8"/>
-      <c r="AE43" s="6"/>
+      <c r="O43" s="5">
+        <v>52837.199999999997</v>
+      </c>
+      <c r="P43" s="5">
+        <v>52837.199999999997</v>
+      </c>
+      <c r="Q43" s="6">
+        <v>0.12638140391568298</v>
+      </c>
+      <c r="R43" s="7">
+        <v>672</v>
+      </c>
+      <c r="S43" s="6">
+        <v>0.090909090909090828</v>
+      </c>
+      <c r="T43" s="6">
+        <v>0.31008346152830968</v>
+      </c>
+      <c r="U43" s="6">
+        <v>-0.061443853307498068</v>
+      </c>
+      <c r="V43" s="6">
+        <v>0.011382935596152322</v>
+      </c>
+      <c r="W43" s="6">
+        <v>-0.0013119202039569102</v>
+      </c>
+      <c r="X43" s="8">
+        <v>31.615981604696675</v>
+      </c>
+      <c r="Y43" s="6">
+        <v>0.42465753424657532</v>
+      </c>
+      <c r="Z43" s="6">
+        <v>0.17221135029354206</v>
+      </c>
+      <c r="AA43" s="8">
+        <v>9.1141006220839813</v>
+      </c>
+      <c r="AB43" s="8">
+        <v>7.2484427435387673</v>
+      </c>
+      <c r="AC43" s="8">
+        <v>17.063419</v>
+      </c>
+      <c r="AD43" s="8">
+        <v>23.779582387475536</v>
+      </c>
+      <c r="AE43" s="6">
+        <v>0.59491193737769077</v>
+      </c>
       <c r="AF43" s="9"/>
-      <c r="AG43" s="5"/>
+      <c r="AG43" s="5">
+        <v>-582.08000000000004</v>
+      </c>
       <c r="AH43" s="10">
         <v>2</v>
       </c>
@@ -6972,13 +7083,13 @@
         <v>52</v>
       </c>
       <c r="O44" s="5">
-        <v>49410.950000000004</v>
+        <v>44391.18</v>
       </c>
       <c r="P44" s="5">
-        <v>49410.950000000004</v>
+        <v>44391.18</v>
       </c>
       <c r="Q44" s="6">
-        <v>0.32520835221917865</v>
+        <v>0.19057744287177147</v>
       </c>
       <c r="R44" s="7">
         <v>552</v>
@@ -7103,13 +7214,13 @@
         <v>52</v>
       </c>
       <c r="O45" s="5">
-        <v>31487.409999999996</v>
+        <v>28541.02</v>
       </c>
       <c r="P45" s="5">
-        <v>31487.409999999996</v>
+        <v>28541.02</v>
       </c>
       <c r="Q45" s="6">
-        <v>0.26451094460191316</v>
+        <v>0.14618611566026241</v>
       </c>
       <c r="R45" s="7">
         <v>361</v>
@@ -7232,13 +7343,13 @@
         <v>52</v>
       </c>
       <c r="O46" s="5">
-        <v>28066.539999999997</v>
+        <v>25469.700000000001</v>
       </c>
       <c r="P46" s="5">
-        <v>28066.539999999997</v>
+        <v>25469.700000000001</v>
       </c>
       <c r="Q46" s="6">
-        <v>0.016041460470861413</v>
+        <v>-0.077967174231141412</v>
       </c>
       <c r="R46" s="7">
         <v>331</v>
@@ -7361,13 +7472,13 @@
         <v>52</v>
       </c>
       <c r="O47" s="5">
-        <v>53289.279999999999</v>
+        <v>50241.110000000001</v>
       </c>
       <c r="P47" s="5">
-        <v>53289.279999999992</v>
+        <v>50241.110000000001</v>
       </c>
       <c r="Q47" s="6">
-        <v>-0.10493348049193896</v>
+        <v>-0.15613167481486623</v>
       </c>
       <c r="R47" s="7">
         <v>522</v>
@@ -7492,13 +7603,13 @@
         <v>52</v>
       </c>
       <c r="O48" s="5">
-        <v>53554.199999999997</v>
+        <v>43201.970000000001</v>
       </c>
       <c r="P48" s="5">
-        <v>53554.199999999997</v>
+        <v>43201.970000000008</v>
       </c>
       <c r="Q48" s="6">
-        <v>0.24327453992002801</v>
+        <v>0.0029448554060906851</v>
       </c>
       <c r="R48" s="7">
         <v>603</v>
@@ -7621,13 +7732,13 @@
         <v>52</v>
       </c>
       <c r="O49" s="5">
-        <v>40070.079999999994</v>
+        <v>36041.879999999997</v>
       </c>
       <c r="P49" s="5">
-        <v>40070.079999999994</v>
+        <v>36041.879999999997</v>
       </c>
       <c r="Q49" s="6">
-        <v>0.032418441167209933</v>
+        <v>-0.071369421614939532</v>
       </c>
       <c r="R49" s="7">
         <v>449</v>
@@ -7751,9 +7862,15 @@
       <c t="s" r="N50" s="4">
         <v>52</v>
       </c>
-      <c r="O50" s="5"/>
-      <c r="P50" s="5"/>
-      <c r="Q50" s="6"/>
+      <c r="O50" s="5">
+        <v>22836.049999999999</v>
+      </c>
+      <c r="P50" s="5">
+        <v>22836.049999999999</v>
+      </c>
+      <c r="Q50" s="6">
+        <v>0.52554391974945736</v>
+      </c>
       <c r="R50" s="7"/>
       <c r="S50" s="6"/>
       <c r="T50" s="6"/>
@@ -7845,13 +7962,13 @@
         <v>52</v>
       </c>
       <c r="O51" s="5">
-        <v>50504.62999999999</v>
+        <v>45148.440000000002</v>
       </c>
       <c r="P51" s="5">
-        <v>50504.62999999999</v>
+        <v>45148.440000000002</v>
       </c>
       <c r="Q51" s="6">
-        <v>0.17089215657635615</v>
+        <v>0.046715009646803418</v>
       </c>
       <c r="R51" s="7">
         <v>582</v>
@@ -7939,7 +8056,7 @@
         <v>19642</v>
       </c>
       <c r="B52" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C52" s="4">
         <v>44</v>
@@ -7976,55 +8093,55 @@
         <v>52</v>
       </c>
       <c r="O52" s="5">
-        <v>20109.630000000001</v>
+        <v>26031.099999999999</v>
       </c>
       <c r="P52" s="5">
-        <v>23461.235000000001</v>
+        <v>26031.099999999999</v>
       </c>
       <c r="Q52" s="6">
-        <v>-0.066509674007801056</v>
+        <v>0.035741725656621703</v>
       </c>
       <c r="R52" s="7">
-        <v>280</v>
+        <v>327</v>
       </c>
       <c r="S52" s="6">
-        <v>0.057268722466960131</v>
+        <v>-0.0090909090909090384</v>
       </c>
       <c r="T52" s="6">
-        <v>0.31879997792102588</v>
+        <v>0.33688077916872061</v>
       </c>
       <c r="U52" s="6">
-        <v>-0.023318698553876922</v>
+        <v>-0.0037361349605739037</v>
       </c>
       <c r="V52" s="6">
-        <v>0.032810648430627511</v>
+        <v>0.028774604068823682</v>
       </c>
       <c r="W52" s="6">
-        <v>-0.017532396170391994</v>
+        <v>-0.016068765900895777</v>
       </c>
       <c r="X52" s="8">
-        <v>23.928754198473282</v>
+        <v>24.978966844919785</v>
       </c>
       <c r="Y52" s="6">
-        <v>0.66412213740458015</v>
+        <v>0.52941176470588236</v>
       </c>
       <c r="Z52" s="6">
-        <v>0.030534351145038167</v>
+        <v>0.026737967914438502</v>
       </c>
       <c r="AA52" s="8">
-        <v>4.0774999999999997</v>
+        <v>4.76518868501529</v>
       </c>
       <c r="AB52" s="8">
-        <v>4.5287526717557256</v>
+        <v>4.8053758064516128</v>
       </c>
       <c r="AC52" s="8">
-        <v>9.0015470000000004</v>
+        <v>10.032025000000001</v>
       </c>
       <c r="AD52" s="8">
-        <v>15.89223893129771</v>
+        <v>16.923172727272728</v>
       </c>
       <c r="AE52" s="6">
-        <v>0.8854961832061069</v>
+        <v>0.81283422459893051</v>
       </c>
       <c r="AF52" s="9"/>
       <c r="AG52" s="5">
@@ -8105,13 +8222,13 @@
         <v>52</v>
       </c>
       <c r="O53" s="5">
-        <v>33502.190000000002</v>
+        <v>29900.939999999999</v>
       </c>
       <c r="P53" s="5">
-        <v>33502.190000000002</v>
+        <v>29900.939999999999</v>
       </c>
       <c r="Q53" s="6">
-        <v>-0.053806907322914488</v>
+        <v>-0.15551601574249418</v>
       </c>
       <c r="R53" s="7">
         <v>350</v>
@@ -8236,13 +8353,13 @@
         <v>52</v>
       </c>
       <c r="O54" s="5">
-        <v>38383.399999999994</v>
+        <v>34712.220000000001</v>
       </c>
       <c r="P54" s="5">
-        <v>38383.399999999987</v>
+        <v>34712.220000000001</v>
       </c>
       <c r="Q54" s="6">
-        <v>0.098519419719452994</v>
+        <v>-0.0065484617940568812</v>
       </c>
       <c r="R54" s="7">
         <v>429</v>
@@ -8251,10 +8368,10 @@
         <v>-0.033783783783783772</v>
       </c>
       <c r="T54" s="6">
-        <v>0.34972596487023033</v>
+        <v>0.25747990016517558</v>
       </c>
       <c r="U54" s="6">
-        <v>-0.0032234872366700184</v>
+        <v>-0.095469551941724809</v>
       </c>
       <c r="V54" s="6">
         <v>0.014136540796281726</v>
@@ -8365,13 +8482,13 @@
         <v>52</v>
       </c>
       <c r="O55" s="5">
-        <v>55698.099999999999</v>
+        <v>49419.550000000003</v>
       </c>
       <c r="P55" s="5">
-        <v>55698.099999999999</v>
+        <v>49419.550000000003</v>
       </c>
       <c r="Q55" s="6">
-        <v>0.10953429245253887</v>
+        <v>-0.015537595670716442</v>
       </c>
       <c r="R55" s="7">
         <v>624</v>
@@ -8494,13 +8611,13 @@
         <v>52</v>
       </c>
       <c r="O56" s="5">
-        <v>97997.449999999983</v>
+        <v>86670.139999999999</v>
       </c>
       <c r="P56" s="5">
-        <v>97997.449999999983</v>
+        <v>86670.139999999999</v>
       </c>
       <c r="Q56" s="6">
-        <v>0.0021356270428629642</v>
+        <v>-0.11369902895643991</v>
       </c>
       <c r="R56" s="7">
         <v>986</v>
@@ -8623,13 +8740,13 @@
         <v>52</v>
       </c>
       <c r="O57" s="5">
-        <v>38354.859999999993</v>
+        <v>34200.25</v>
       </c>
       <c r="P57" s="5">
-        <v>38354.859999999993</v>
+        <v>34200.25</v>
       </c>
       <c r="Q57" s="6">
-        <v>0.069136640091697066</v>
+        <v>-0.046672563130302991</v>
       </c>
       <c r="R57" s="7">
         <v>462</v>
@@ -8751,9 +8868,15 @@
       <c t="s" r="N58" s="4">
         <v>52</v>
       </c>
-      <c r="O58" s="5"/>
-      <c r="P58" s="5"/>
-      <c r="Q58" s="6"/>
+      <c r="O58" s="5">
+        <v>16826.759999999998</v>
+      </c>
+      <c r="P58" s="5">
+        <v>16826.759999999998</v>
+      </c>
+      <c r="Q58" s="6">
+        <v>-0.34099771713371629</v>
+      </c>
       <c r="R58" s="7"/>
       <c r="S58" s="6"/>
       <c r="T58" s="6"/>
@@ -8845,13 +8968,13 @@
         <v>52</v>
       </c>
       <c r="O59" s="5">
-        <v>37571.270000000004</v>
+        <v>33893.699999999997</v>
       </c>
       <c r="P59" s="5">
-        <v>37571.270000000004</v>
+        <v>33893.699999999997</v>
       </c>
       <c r="Q59" s="6">
-        <v>0.32375099665532514</v>
+        <v>0.19417893393906005</v>
       </c>
       <c r="R59" s="7">
         <v>390</v>
@@ -8974,13 +9097,13 @@
         <v>52</v>
       </c>
       <c r="O60" s="5">
-        <v>55544.770000000004</v>
+        <v>49359.809999999998</v>
       </c>
       <c r="P60" s="5">
-        <v>55544.770000000004</v>
+        <v>49359.809999999998</v>
       </c>
       <c r="Q60" s="6">
-        <v>-0.023764392043220561</v>
+        <v>-0.13246910332005846</v>
       </c>
       <c r="R60" s="7">
         <v>631</v>
@@ -9103,13 +9226,13 @@
         <v>52</v>
       </c>
       <c r="O61" s="5">
-        <v>55279.610000000001</v>
+        <v>46606.230000000003</v>
       </c>
       <c r="P61" s="5">
-        <v>55279.610000000001</v>
+        <v>46606.230000000003</v>
       </c>
       <c r="Q61" s="6">
-        <v>0.31844986599560698</v>
+        <v>0.11158486281036439</v>
       </c>
       <c r="R61" s="7">
         <v>532</v>
@@ -9234,13 +9357,13 @@
         <v>52</v>
       </c>
       <c r="O62" s="5">
-        <v>48410</v>
+        <v>42786.389999999999</v>
       </c>
       <c r="P62" s="5">
-        <v>48410</v>
+        <v>42786.389999999999</v>
       </c>
       <c r="Q62" s="6">
-        <v>0.049159437125203542</v>
+        <v>-0.072717520160722193</v>
       </c>
       <c r="R62" s="7">
         <v>526</v>
@@ -9363,13 +9486,13 @@
         <v>52</v>
       </c>
       <c r="O63" s="5">
-        <v>53105.809999999998</v>
+        <v>47500.550000000003</v>
       </c>
       <c r="P63" s="5">
-        <v>53105.809999999998</v>
+        <v>47500.550000000003</v>
       </c>
       <c r="Q63" s="6">
-        <v>0.25659456590590657</v>
+        <v>0.12396238768492207</v>
       </c>
       <c r="R63" s="7">
         <v>564</v>
@@ -9496,13 +9619,13 @@
         <v>52</v>
       </c>
       <c r="O64" s="5">
-        <v>12718.470000000001</v>
+        <v>11839.4</v>
       </c>
       <c r="P64" s="5">
-        <v>12718.470000000001</v>
+        <v>11839.4</v>
       </c>
       <c r="Q64" s="6">
-        <v>-0.17247080363922407</v>
+        <v>-0.22966762767897642</v>
       </c>
       <c r="R64" s="7">
         <v>164</v>
@@ -9627,13 +9750,13 @@
         <v>52</v>
       </c>
       <c r="O65" s="5">
-        <v>56592.37999999999</v>
+        <v>50631.82</v>
       </c>
       <c r="P65" s="5">
-        <v>56592.37999999999</v>
+        <v>50631.82</v>
       </c>
       <c r="Q65" s="6">
-        <v>0.47087445383834248</v>
+        <v>0.31595544469664061</v>
       </c>
       <c r="R65" s="7">
         <v>589</v>
@@ -9757,9 +9880,15 @@
       <c t="s" r="N66" s="4">
         <v>52</v>
       </c>
-      <c r="O66" s="5"/>
-      <c r="P66" s="5"/>
-      <c r="Q66" s="6"/>
+      <c r="O66" s="5">
+        <v>29502.82</v>
+      </c>
+      <c r="P66" s="5">
+        <v>29502.82</v>
+      </c>
+      <c r="Q66" s="6">
+        <v>0.010004248459206222</v>
+      </c>
       <c r="R66" s="7"/>
       <c r="S66" s="6"/>
       <c r="T66" s="6"/>
@@ -9851,13 +9980,13 @@
         <v>52</v>
       </c>
       <c r="O67" s="5">
-        <v>26353.790000000001</v>
+        <v>23716.23</v>
       </c>
       <c r="P67" s="5">
-        <v>26353.790000000001</v>
+        <v>23716.23</v>
       </c>
       <c r="Q67" s="6">
-        <v>-0.14625925819141194</v>
+        <v>-0.23170398667124958</v>
       </c>
       <c r="R67" s="7">
         <v>292</v>
@@ -9982,13 +10111,13 @@
         <v>52</v>
       </c>
       <c r="O68" s="5">
-        <v>34514.839999999997</v>
+        <v>31730.639999999999</v>
       </c>
       <c r="P68" s="5">
-        <v>34514.839999999997</v>
+        <v>31730.639999999996</v>
       </c>
       <c r="Q68" s="6">
-        <v>0.59891524343325275</v>
+        <v>0.46993594581035003</v>
       </c>
       <c r="R68" s="7">
         <v>446</v>
@@ -10113,13 +10242,13 @@
         <v>52</v>
       </c>
       <c r="O69" s="5">
-        <v>30691.200000000004</v>
+        <v>28426.18</v>
       </c>
       <c r="P69" s="5">
-        <v>30691.200000000004</v>
+        <v>28426.18</v>
       </c>
       <c r="Q69" s="6">
-        <v>-0.16278628234358283</v>
+        <v>-0.22457291221684095</v>
       </c>
       <c r="R69" s="7">
         <v>347</v>
@@ -10244,13 +10373,13 @@
         <v>52</v>
       </c>
       <c r="O70" s="5">
-        <v>44123.419999999998</v>
+        <v>41386.449999999997</v>
       </c>
       <c r="P70" s="5">
-        <v>44123.419999999998</v>
+        <v>41386.449999999997</v>
       </c>
       <c r="Q70" s="6">
-        <v>-0.02453657472184767</v>
+        <v>-0.085044444036681988</v>
       </c>
       <c r="R70" s="7">
         <v>416</v>
@@ -10373,13 +10502,13 @@
         <v>52</v>
       </c>
       <c r="O71" s="5">
-        <v>60353.120000000003</v>
+        <v>50782.830000000002</v>
       </c>
       <c r="P71" s="5">
-        <v>60353.120000000003</v>
+        <v>50782.830000000002</v>
       </c>
       <c r="Q71" s="6">
-        <v>0.097569722535624237</v>
+        <v>-0.07647364986808014</v>
       </c>
       <c r="R71" s="7">
         <v>555</v>
@@ -10467,7 +10596,7 @@
         <v>19693</v>
       </c>
       <c r="B72" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c t="s" r="C72" s="4">
         <v>44</v>
@@ -10502,59 +10631,59 @@
         <v>52</v>
       </c>
       <c r="O72" s="5">
-        <v>3328.5300000000002</v>
+        <v>43046.470000000001</v>
       </c>
       <c r="P72" s="5">
-        <v>23299.710000000003</v>
+        <v>43046.470000000008</v>
       </c>
       <c r="Q72" s="6">
-        <v>-0.5778368088848882</v>
+        <v>-0.22004887007430873</v>
       </c>
       <c r="R72" s="7">
-        <v>273</v>
+        <v>486</v>
       </c>
       <c r="S72" s="6">
-        <v>0.21875</v>
+        <v>-0.23824451410658309</v>
       </c>
       <c r="T72" s="6">
-        <v>0.0002763982899357975</v>
+        <v>1.8896754092225611E-05</v>
       </c>
       <c r="U72" s="6">
-        <v>-0.31979883011419452</v>
+        <v>-0.33810462680861969</v>
       </c>
       <c r="V72" s="6">
-        <v>0.035243485863128768</v>
+        <v>0.024410313437584534</v>
       </c>
       <c r="W72" s="6">
-        <v>0.0028237690512027827</v>
+        <v>0.0049337165540290035</v>
       </c>
       <c r="X72" s="8">
-        <v>27.681250000000002</v>
+        <v>34.408365637065636</v>
       </c>
       <c r="Y72" s="6">
-        <v>0.75</v>
+        <v>0.6216216216216216</v>
       </c>
       <c r="Z72" s="6">
-        <v>0.041666666666666664</v>
+        <v>0.30501930501930502</v>
       </c>
       <c r="AA72" s="8">
-        <v>4.4210526315789478</v>
+        <v>5.9947786307053939</v>
       </c>
       <c r="AB72" s="8">
-        <v>8.2015136363636358</v>
+        <v>12.096082071713147</v>
       </c>
       <c r="AC72" s="8">
-        <v>12.49137</v>
+        <v>17.993400000000001</v>
       </c>
       <c r="AD72" s="8">
-        <v>19.111804166666666</v>
+        <v>25.467631274131275</v>
       </c>
       <c r="AE72" s="6">
-        <v>0.58333333333333337</v>
+        <v>0.38610038610038611</v>
       </c>
       <c r="AF72" s="9"/>
       <c r="AG72" s="5">
-        <v>0</v>
+        <v>-76.700000000000003</v>
       </c>
       <c r="AH72" s="10">
         <v>2</v>
@@ -10633,13 +10762,13 @@
         <v>52</v>
       </c>
       <c r="O73" s="5">
-        <v>49657.710000000006</v>
+        <v>43558.550000000003</v>
       </c>
       <c r="P73" s="5">
-        <v>49657.710000000006</v>
+        <v>43558.550000000003</v>
       </c>
       <c r="Q73" s="6">
-        <v>0.35078986496374798</v>
+        <v>0.18488041177325054</v>
       </c>
       <c r="R73" s="7">
         <v>499.00000000000006</v>
@@ -10764,13 +10893,13 @@
         <v>52</v>
       </c>
       <c r="O74" s="5">
-        <v>52754.050000000003</v>
+        <v>47285.059999999998</v>
       </c>
       <c r="P74" s="5">
-        <v>52754.050000000003</v>
+        <v>47285.059999999998</v>
       </c>
       <c r="Q74" s="6">
-        <v>0.13555848398328929</v>
+        <v>0.017835617334761356</v>
       </c>
       <c r="R74" s="7">
         <v>593</v>
@@ -10895,13 +11024,13 @@
         <v>52</v>
       </c>
       <c r="O75" s="5">
-        <v>33136.520000000004</v>
+        <v>29519.91</v>
       </c>
       <c r="P75" s="5">
-        <v>33136.520000000004</v>
+        <v>29519.91</v>
       </c>
       <c r="Q75" s="6">
-        <v>-0.0018029079685518701</v>
+        <v>-0.11074885597431283</v>
       </c>
       <c r="R75" s="7">
         <v>389</v>
@@ -11024,13 +11153,13 @@
         <v>52</v>
       </c>
       <c r="O76" s="5">
-        <v>50199.120000000003</v>
+        <v>44957.970000000001</v>
       </c>
       <c r="P76" s="5">
-        <v>50199.120000000003</v>
+        <v>44957.970000000008</v>
       </c>
       <c r="Q76" s="6">
-        <v>0.29193576032781787</v>
+        <v>0.15704835373100612</v>
       </c>
       <c r="R76" s="7">
         <v>546</v>
@@ -11154,9 +11283,15 @@
       <c t="s" r="N77" s="4">
         <v>52</v>
       </c>
-      <c r="O77" s="5"/>
-      <c r="P77" s="5"/>
-      <c r="Q77" s="6"/>
+      <c r="O77" s="5">
+        <v>32899.32</v>
+      </c>
+      <c r="P77" s="5">
+        <v>32899.32</v>
+      </c>
+      <c r="Q77" s="6">
+        <v>0.073111382783153767</v>
+      </c>
       <c r="R77" s="7"/>
       <c r="S77" s="6"/>
       <c r="T77" s="6"/>
@@ -11248,13 +11383,13 @@
         <v>52</v>
       </c>
       <c r="O78" s="5">
-        <v>47748.430000000008</v>
+        <v>44813.239999999998</v>
       </c>
       <c r="P78" s="5">
-        <v>47748.430000000008</v>
+        <v>44813.239999999998</v>
       </c>
       <c r="Q78" s="6">
-        <v>0.058430616095590526</v>
+        <v>-0.0066331977315369217</v>
       </c>
       <c r="R78" s="7">
         <v>508</v>
@@ -11379,13 +11514,13 @@
         <v>52</v>
       </c>
       <c r="O79" s="5">
-        <v>30552.130000000005</v>
+        <v>28899.25</v>
       </c>
       <c r="P79" s="5">
-        <v>30552.130000000005</v>
+        <v>28899.25</v>
       </c>
       <c r="Q79" s="6">
-        <v>-0.030754198318293069</v>
+        <v>-0.083190706040788043</v>
       </c>
       <c r="R79" s="7">
         <v>306</v>
@@ -11434,7 +11569,7 @@
         <v>0</v>
       </c>
       <c r="AH79" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI79" s="11"/>
       <c r="AJ79" s="12">
@@ -11510,13 +11645,13 @@
         <v>52</v>
       </c>
       <c r="O80" s="5">
-        <v>34959.75</v>
+        <v>31557.59</v>
       </c>
       <c r="P80" s="5">
-        <v>34959.75</v>
+        <v>31557.59</v>
       </c>
       <c r="Q80" s="6">
-        <v>-0.068452944013514871</v>
+        <v>-0.15910782947450863</v>
       </c>
       <c r="R80" s="7">
         <v>312</v>
@@ -11641,13 +11776,13 @@
         <v>52</v>
       </c>
       <c r="O81" s="5">
-        <v>45643.419999999998</v>
+        <v>39449.279999999999</v>
       </c>
       <c r="P81" s="5">
-        <v>45643.419999999998</v>
+        <v>39449.279999999992</v>
       </c>
       <c r="Q81" s="6">
-        <v>0.42936524215810445</v>
+        <v>0.23539011012239808</v>
       </c>
       <c r="R81" s="7">
         <v>469</v>
@@ -11770,13 +11905,13 @@
         <v>52</v>
       </c>
       <c r="O82" s="5">
-        <v>31839.389999999999</v>
+        <v>28841.130000000001</v>
       </c>
       <c r="P82" s="5">
-        <v>31839.389999999996</v>
+        <v>28841.130000000001</v>
       </c>
       <c r="Q82" s="6">
-        <v>0.16833694837312208</v>
+        <v>0.058316689227793095</v>
       </c>
       <c r="R82" s="7">
         <v>347</v>
@@ -11864,7 +11999,7 @@
         <v>19719</v>
       </c>
       <c r="B83" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c t="s" r="C83" s="4">
         <v>44</v>
@@ -11901,55 +12036,55 @@
         <v>52</v>
       </c>
       <c r="O83" s="5">
-        <v>5921.8700000000008</v>
+        <v>27451.18</v>
       </c>
       <c r="P83" s="5">
-        <v>20726.545000000002</v>
+        <v>27451.18</v>
       </c>
       <c r="Q83" s="6">
-        <v>-0.43022313795132028</v>
+        <v>-0.24536157859722996</v>
       </c>
       <c r="R83" s="7">
-        <v>192.5</v>
+        <v>307</v>
       </c>
       <c r="S83" s="6">
-        <v>-0.30379746835443033</v>
+        <v>-0.26378896882494007</v>
       </c>
       <c r="T83" s="6">
-        <v>0.19924650490470072</v>
+        <v>0.27839235247975802</v>
       </c>
       <c r="U83" s="6">
-        <v>-0.19062696411775334</v>
+        <v>-0.062213332151698865</v>
       </c>
       <c r="V83" s="6">
-        <v>0.01407908312745805</v>
+        <v>0.016357970299256824</v>
       </c>
       <c r="W83" s="6">
-        <v>-0.012647271892155688</v>
+        <v>-0.00471154194165319</v>
       </c>
       <c r="X83" s="8">
-        <v>35.102313888888887</v>
+        <v>38.822896116504857</v>
       </c>
       <c r="Y83" s="6">
-        <v>0.3611111111111111</v>
+        <v>0.20388349514563106</v>
       </c>
       <c r="Z83" s="6">
-        <v>0.33333333333333331</v>
+        <v>0.38349514563106796</v>
       </c>
       <c r="AA83" s="8">
-        <v>7.5983050847457632</v>
+        <v>13.082529581993569</v>
       </c>
       <c r="AB83" s="8">
-        <v>15.045833333333334</v>
+        <v>9.6988101190476197</v>
       </c>
       <c r="AC83" s="8">
-        <v>23.405042999999999</v>
+        <v>23.061046999999999</v>
       </c>
       <c r="AD83" s="8">
-        <v>23.916202777777777</v>
+        <v>27.389724757281552</v>
       </c>
       <c r="AE83" s="6">
-        <v>0.58333333333333337</v>
+        <v>0.37378640776699029</v>
       </c>
       <c r="AF83" s="9"/>
       <c r="AG83" s="5">
@@ -12032,13 +12167,13 @@
         <v>52</v>
       </c>
       <c r="O84" s="5">
-        <v>35768.410000000003</v>
+        <v>31430.970000000001</v>
       </c>
       <c r="P84" s="5">
-        <v>35768.410000000003</v>
+        <v>31430.970000000001</v>
       </c>
       <c r="Q84" s="6">
-        <v>0.26769599036550762</v>
+        <v>0.11396941162043706</v>
       </c>
       <c r="R84" s="7">
         <v>360</v>
@@ -12163,13 +12298,13 @@
         <v>52</v>
       </c>
       <c r="O85" s="5">
-        <v>41589.400000000001</v>
+        <v>39339.410000000003</v>
       </c>
       <c r="P85" s="5">
-        <v>41589.400000000001</v>
+        <v>39339.409999999996</v>
       </c>
       <c r="Q85" s="6">
-        <v>0.013250407535241981</v>
+        <v>-0.041566523809048128</v>
       </c>
       <c r="R85" s="7">
         <v>482</v>
@@ -12292,13 +12427,13 @@
         <v>52</v>
       </c>
       <c r="O86" s="5">
-        <v>38238.889999999999</v>
+        <v>34632.75</v>
       </c>
       <c r="P86" s="5">
-        <v>38238.889999999999</v>
+        <v>34632.75</v>
       </c>
       <c r="Q86" s="6">
-        <v>0.115307278407911</v>
+        <v>0.010127599056394931</v>
       </c>
       <c r="R86" s="7">
         <v>359</v>
@@ -12423,13 +12558,13 @@
         <v>52</v>
       </c>
       <c r="O87" s="5">
-        <v>20705.259999999998</v>
+        <v>19583.029999999999</v>
       </c>
       <c r="P87" s="5">
-        <v>20705.259999999998</v>
+        <v>19583.029999999999</v>
       </c>
       <c r="Q87" s="6">
-        <v>0.21127734480575899</v>
+        <v>0.14562582559463277</v>
       </c>
       <c r="R87" s="7">
         <v>265</v>
@@ -12554,13 +12689,13 @@
         <v>52</v>
       </c>
       <c r="O88" s="5">
-        <v>33648.82</v>
+        <v>30466.84</v>
       </c>
       <c r="P88" s="5">
-        <v>33648.82</v>
+        <v>30466.84</v>
       </c>
       <c r="Q88" s="6">
-        <v>0.14577765277258981</v>
+        <v>0.037427892645211847</v>
       </c>
       <c r="R88" s="7">
         <v>382</v>
@@ -12684,9 +12819,15 @@
       <c t="s" r="N89" s="4">
         <v>52</v>
       </c>
-      <c r="O89" s="5"/>
-      <c r="P89" s="5"/>
-      <c r="Q89" s="6"/>
+      <c r="O89" s="5">
+        <v>82900.139999999999</v>
+      </c>
+      <c r="P89" s="5">
+        <v>82900.139999999999</v>
+      </c>
+      <c r="Q89" s="6">
+        <v>-0.071762595566861931</v>
+      </c>
       <c r="R89" s="7"/>
       <c r="S89" s="6"/>
       <c r="T89" s="6"/>
@@ -12776,13 +12917,13 @@
         <v>52</v>
       </c>
       <c r="O90" s="5">
-        <v>62360.949999999997</v>
+        <v>54325.900000000001</v>
       </c>
       <c r="P90" s="5">
-        <v>62360.949999999997</v>
+        <v>54325.900000000001</v>
       </c>
       <c r="Q90" s="6">
-        <v>0.063079402263901851</v>
+        <v>-0.073895678313936619</v>
       </c>
       <c r="R90" s="7">
         <v>640</v>
@@ -12906,9 +13047,15 @@
       <c t="s" r="N91" s="4">
         <v>52</v>
       </c>
-      <c r="O91" s="5"/>
-      <c r="P91" s="5"/>
-      <c r="Q91" s="6"/>
+      <c r="O91" s="5">
+        <v>41904.300000000003</v>
+      </c>
+      <c r="P91" s="5">
+        <v>41904.300000000003</v>
+      </c>
+      <c r="Q91" s="6">
+        <v>-0.0012384325962322418</v>
+      </c>
       <c r="R91" s="7"/>
       <c r="S91" s="6"/>
       <c r="T91" s="6"/>
@@ -13000,13 +13147,13 @@
         <v>52</v>
       </c>
       <c r="O92" s="5">
-        <v>14839.65</v>
+        <v>13752.16</v>
       </c>
       <c r="P92" s="5">
-        <v>14839.65</v>
+        <v>13752.16</v>
       </c>
       <c r="Q92" s="6">
-        <v>-0.27091250596328043</v>
+        <v>-0.32434202477875063</v>
       </c>
       <c r="R92" s="7">
         <v>161</v>
@@ -13129,13 +13276,13 @@
         <v>52</v>
       </c>
       <c r="O93" s="5">
-        <v>54663.669999999998</v>
+        <v>48367.080000000002</v>
       </c>
       <c r="P93" s="5">
-        <v>54663.669999999998</v>
+        <v>48367.080000000002</v>
       </c>
       <c r="Q93" s="6">
-        <v>-0.078019200065846395</v>
+        <v>-0.18422017568745019</v>
       </c>
       <c r="R93" s="7">
         <v>634</v>
@@ -13258,13 +13405,13 @@
         <v>52</v>
       </c>
       <c r="O94" s="5">
-        <v>90321.420000000013</v>
+        <v>83311.270000000004</v>
       </c>
       <c r="P94" s="5">
-        <v>90321.420000000013</v>
+        <v>83311.270000000004</v>
       </c>
       <c r="Q94" s="6">
-        <v>0.082042109129514929</v>
+        <v>-0.0019388279650774942</v>
       </c>
       <c r="R94" s="7">
         <v>806</v>
@@ -13389,13 +13536,13 @@
         <v>52</v>
       </c>
       <c r="O95" s="5">
-        <v>53650.770000000004</v>
+        <v>47293.410000000003</v>
       </c>
       <c r="P95" s="5">
-        <v>53650.770000000004</v>
+        <v>47293.409999999996</v>
       </c>
       <c r="Q95" s="6">
-        <v>0.44413109776613768</v>
+        <v>0.27300846009114177</v>
       </c>
       <c r="R95" s="7">
         <v>473</v>
@@ -13520,13 +13667,13 @@
         <v>52</v>
       </c>
       <c r="O96" s="5">
-        <v>31323.480000000003</v>
+        <v>28406.810000000001</v>
       </c>
       <c r="P96" s="5">
-        <v>31323.480000000003</v>
+        <v>28406.810000000001</v>
       </c>
       <c r="Q96" s="6">
-        <v>0.092628714943491008</v>
+        <v>-0.0091108553090553102</v>
       </c>
       <c r="R96" s="7">
         <v>345</v>
@@ -13614,7 +13761,7 @@
         <v>19742</v>
       </c>
       <c r="B97" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c t="s" r="C97" s="4">
         <v>44</v>
@@ -13649,59 +13796,59 @@
         <v>52</v>
       </c>
       <c r="O97" s="5">
-        <v>7759.6999999999998</v>
+        <v>28183.02</v>
       </c>
       <c r="P97" s="5">
-        <v>18105.966666666667</v>
+        <v>28183.02</v>
       </c>
       <c r="Q97" s="6">
-        <v>-0.42078848322610252</v>
+        <v>-0.098422632605324134</v>
       </c>
       <c r="R97" s="7">
-        <v>165.66666666666669</v>
+        <v>290</v>
       </c>
       <c r="S97" s="6">
-        <v>-0.31730769230769218</v>
+        <v>-0.13946587537091992</v>
       </c>
       <c r="T97" s="6">
-        <v>0.22723870768199803</v>
+        <v>0.26198310436332722</v>
       </c>
       <c r="U97" s="6">
-        <v>-0.055321185097362016</v>
+        <v>-0.019297844110117205</v>
       </c>
       <c r="V97" s="6">
-        <v>0.02631905872649716</v>
+        <v>0.01425588951371913</v>
       </c>
       <c r="W97" s="6">
-        <v>-0.012926015180999267</v>
+        <v>-0.010349723132265393</v>
       </c>
       <c r="X97" s="8">
-        <v>38.17479512195122</v>
+        <v>39.547221839080457</v>
       </c>
       <c r="Y97" s="6">
-        <v>0.75609756097560976</v>
+        <v>0.58620689655172409</v>
       </c>
       <c r="Z97" s="6">
-        <v>0.34146341463414637</v>
+        <v>0.40229885057471265</v>
       </c>
       <c r="AA97" s="8">
-        <v>9.0309528571428572</v>
+        <v>10.915610211267605</v>
       </c>
       <c r="AB97" s="8">
-        <v>17.789473684210527</v>
+        <v>15.497006586826348</v>
       </c>
       <c r="AC97" s="8">
-        <v>26.226870999999999</v>
+        <v>25.995951000000002</v>
       </c>
       <c r="AD97" s="8">
-        <v>32.098373170731712</v>
+        <v>33.086781034482762</v>
       </c>
       <c r="AE97" s="6">
-        <v>0.53658536585365857</v>
+        <v>0.32758620689655171</v>
       </c>
       <c r="AF97" s="9"/>
       <c r="AG97" s="5">
-        <v>-375.69999999999999</v>
+        <v>-1178.8</v>
       </c>
       <c r="AH97" s="10">
         <v>2</v>
@@ -13780,13 +13927,13 @@
         <v>52</v>
       </c>
       <c r="O98" s="5">
-        <v>27781.790000000001</v>
+        <v>26133.5</v>
       </c>
       <c r="P98" s="5">
-        <v>27781.790000000001</v>
+        <v>26133.5</v>
       </c>
       <c r="Q98" s="6">
-        <v>0.0423654092052419</v>
+        <v>-0.019477995425593919</v>
       </c>
       <c r="R98" s="7">
         <v>306</v>
@@ -13911,13 +14058,13 @@
         <v>52</v>
       </c>
       <c r="O99" s="5">
-        <v>51036.800000000003</v>
+        <v>45777.779999999999</v>
       </c>
       <c r="P99" s="5">
-        <v>51036.800000000003</v>
+        <v>45777.779999999992</v>
       </c>
       <c r="Q99" s="6">
-        <v>0.22998972373624138</v>
+        <v>0.1032470487071766</v>
       </c>
       <c r="R99" s="7">
         <v>614</v>
@@ -14040,13 +14187,13 @@
         <v>52</v>
       </c>
       <c r="O100" s="5">
-        <v>31718.230000000003</v>
+        <v>28723.599999999999</v>
       </c>
       <c r="P100" s="5">
-        <v>31718.230000000003</v>
+        <v>28723.599999999999</v>
       </c>
       <c r="Q100" s="6">
-        <v>0.246146042951221</v>
+        <v>0.12849299848426865</v>
       </c>
       <c r="R100" s="7">
         <v>342</v>
@@ -14169,13 +14316,13 @@
         <v>52</v>
       </c>
       <c r="O101" s="5">
-        <v>27214.859999999997</v>
+        <v>24901.709999999999</v>
       </c>
       <c r="P101" s="5">
-        <v>27214.859999999997</v>
+        <v>24901.709999999999</v>
       </c>
       <c r="Q101" s="6">
-        <v>0.59229539206124171</v>
+        <v>0.45695690102559228</v>
       </c>
       <c r="R101" s="7">
         <v>301</v>
@@ -14300,13 +14447,13 @@
         <v>52</v>
       </c>
       <c r="O102" s="5">
-        <v>45803.110000000001</v>
+        <v>40008.839999999997</v>
       </c>
       <c r="P102" s="5">
-        <v>45803.110000000001</v>
+        <v>40008.840000000004</v>
       </c>
       <c r="Q102" s="6">
-        <v>0.074268169320374611</v>
+        <v>-0.061630895731059288</v>
       </c>
       <c r="R102" s="7">
         <v>534</v>
@@ -14431,13 +14578,13 @@
         <v>52</v>
       </c>
       <c r="O103" s="5">
-        <v>66790.630000000005</v>
+        <v>58086.540000000001</v>
       </c>
       <c r="P103" s="5">
-        <v>66790.630000000005</v>
+        <v>58086.540000000001</v>
       </c>
       <c r="Q103" s="6">
-        <v>0.078443207074804899</v>
+        <v>-0.062098463729434283</v>
       </c>
       <c r="R103" s="7">
         <v>673</v>
@@ -14562,13 +14709,13 @@
         <v>52</v>
       </c>
       <c r="O104" s="5">
-        <v>15380.629999999999</v>
+        <v>14067.73</v>
       </c>
       <c r="P104" s="5">
-        <v>15380.629999999999</v>
+        <v>14067.73</v>
       </c>
       <c r="Q104" s="6">
-        <v>-0.40286743889541987</v>
+        <v>-0.45383904015454923</v>
       </c>
       <c r="R104" s="7">
         <v>158</v>
@@ -14693,13 +14840,13 @@
         <v>52</v>
       </c>
       <c r="O105" s="5">
-        <v>34228</v>
+        <v>30594.560000000001</v>
       </c>
       <c r="P105" s="5">
-        <v>34228</v>
+        <v>30594.560000000001</v>
       </c>
       <c r="Q105" s="6">
-        <v>-0.22333551392983664</v>
+        <v>-0.30578157593365729</v>
       </c>
       <c r="R105" s="7">
         <v>343</v>
@@ -14824,13 +14971,13 @@
         <v>52</v>
       </c>
       <c r="O106" s="5">
-        <v>19820.970000000001</v>
+        <v>24261.639999999999</v>
       </c>
       <c r="P106" s="5">
-        <v>19820.970000000001</v>
+        <v>24261.639999999996</v>
       </c>
       <c r="Q106" s="6">
-        <v>-0.2775998390533303</v>
+        <v>-0.11575404024978808</v>
       </c>
       <c r="R106" s="7">
         <v>290</v>
@@ -14955,13 +15102,13 @@
         <v>52</v>
       </c>
       <c r="O107" s="5">
-        <v>27701.909999999996</v>
+        <v>25175.610000000001</v>
       </c>
       <c r="P107" s="5">
-        <v>27701.909999999996</v>
+        <v>25175.610000000004</v>
       </c>
       <c r="Q107" s="6">
-        <v>0.12529018908040057</v>
+        <v>0.022668362474443926</v>
       </c>
       <c r="R107" s="7">
         <v>299</v>
@@ -15086,13 +15233,13 @@
         <v>52</v>
       </c>
       <c r="O108" s="5">
-        <v>24010.560000000001</v>
+        <v>21522.52</v>
       </c>
       <c r="P108" s="5">
-        <v>24010.560000000001</v>
+        <v>21522.52</v>
       </c>
       <c r="Q108" s="6">
-        <v>0.24650276134675231</v>
+        <v>0.11733673063604932</v>
       </c>
       <c r="R108" s="7">
         <v>310</v>
@@ -15217,13 +15364,13 @@
         <v>52</v>
       </c>
       <c r="O109" s="5">
-        <v>26551.799999999999</v>
+        <v>24138.82</v>
       </c>
       <c r="P109" s="5">
-        <v>26551.799999999999</v>
+        <v>24138.82</v>
       </c>
       <c r="Q109" s="6">
-        <v>0.15948851463651281</v>
+        <v>0.054116276368387561</v>
       </c>
       <c r="R109" s="7">
         <v>295</v>
@@ -15348,13 +15495,13 @@
         <v>52</v>
       </c>
       <c r="O110" s="5">
-        <v>36613.5</v>
+        <v>33826.790000000001</v>
       </c>
       <c r="P110" s="5">
-        <v>36613.5</v>
+        <v>33826.790000000001</v>
       </c>
       <c r="Q110" s="6">
-        <v>0.085300431410886057</v>
+        <v>0.0026965403538434796</v>
       </c>
       <c r="R110" s="7">
         <v>345</v>
@@ -15479,13 +15626,13 @@
         <v>52</v>
       </c>
       <c r="O111" s="5">
-        <v>30796.139999999999</v>
+        <v>27455.59</v>
       </c>
       <c r="P111" s="5">
-        <v>30796.139999999996</v>
+        <v>27455.59</v>
       </c>
       <c r="Q111" s="6">
-        <v>0.42659525384534125</v>
+        <v>0.27184817271007389</v>
       </c>
       <c r="R111" s="7">
         <v>300</v>
@@ -15608,13 +15755,13 @@
         <v>52</v>
       </c>
       <c r="O112" s="5">
-        <v>64826.240000000005</v>
+        <v>59883.790000000001</v>
       </c>
       <c r="P112" s="5">
-        <v>64826.240000000005</v>
+        <v>59883.790000000001</v>
       </c>
       <c r="Q112" s="6">
-        <v>0.051510797061568026</v>
+        <v>-0.028657966990410788</v>
       </c>
       <c r="R112" s="7">
         <v>828</v>
@@ -15739,13 +15886,13 @@
         <v>52</v>
       </c>
       <c r="O113" s="5">
-        <v>29380.93</v>
+        <v>27635.790000000001</v>
       </c>
       <c r="P113" s="5">
-        <v>29380.93</v>
+        <v>27635.790000000001</v>
       </c>
       <c r="Q113" s="6">
-        <v>0.028282112762368916</v>
+        <v>-0.032794791415481028</v>
       </c>
       <c r="R113" s="7">
         <v>321</v>
@@ -15870,13 +16017,13 @@
         <v>52</v>
       </c>
       <c r="O114" s="5">
-        <v>26248.68</v>
+        <v>23872.169999999998</v>
       </c>
       <c r="P114" s="5">
-        <v>26248.68</v>
+        <v>23872.170000000002</v>
       </c>
       <c r="Q114" s="6">
-        <v>0.15959681993846964</v>
+        <v>0.054608933364669765</v>
       </c>
       <c r="R114" s="7">
         <v>280</v>
@@ -16001,13 +16148,13 @@
         <v>52</v>
       </c>
       <c r="O115" s="5">
-        <v>26974.02</v>
+        <v>25660.919999999998</v>
       </c>
       <c r="P115" s="5">
-        <v>26974.02</v>
+        <v>25660.920000000002</v>
       </c>
       <c r="Q115" s="6">
-        <v>0.0082652721761005132</v>
+        <v>-0.040817257194547207</v>
       </c>
       <c r="R115" s="7">
         <v>394</v>
@@ -16132,13 +16279,13 @@
         <v>52</v>
       </c>
       <c r="O116" s="5">
-        <v>32162.469999999998</v>
+        <v>27933.639999999999</v>
       </c>
       <c r="P116" s="5">
-        <v>32162.469999999998</v>
+        <v>27933.639999999996</v>
       </c>
       <c r="Q116" s="6">
-        <v>-0.075178796536557679</v>
+        <v>-0.19677740665084009</v>
       </c>
       <c r="R116" s="7">
         <v>297</v>
@@ -16261,13 +16408,13 @@
         <v>52</v>
       </c>
       <c r="O117" s="5">
-        <v>23152.130000000001</v>
+        <v>21206.130000000001</v>
       </c>
       <c r="P117" s="5">
-        <v>23152.130000000001</v>
+        <v>21206.130000000001</v>
       </c>
       <c r="Q117" s="6">
-        <v>0.90877551979461346</v>
+        <v>0.74833770428820778</v>
       </c>
       <c r="R117" s="7">
         <v>256</v>
@@ -16390,13 +16537,13 @@
         <v>52</v>
       </c>
       <c r="O118" s="5">
-        <v>107619.88999999998</v>
+        <v>94515.360000000001</v>
       </c>
       <c r="P118" s="5">
-        <v>107619.88999999998</v>
+        <v>94515.360000000001</v>
       </c>
       <c r="Q118" s="6">
-        <v>0.13496069553904722</v>
+        <v>-0.0032398404725795249</v>
       </c>
       <c r="R118" s="7">
         <v>1053</v>
@@ -16521,13 +16668,13 @@
         <v>52</v>
       </c>
       <c r="O119" s="5">
-        <v>64141.280000000013</v>
+        <v>58859.970000000001</v>
       </c>
       <c r="P119" s="5">
-        <v>64141.280000000013</v>
+        <v>58859.970000000008</v>
       </c>
       <c r="Q119" s="6">
-        <v>-0.047221742756192175</v>
+        <v>-0.1256722716163009</v>
       </c>
       <c r="R119" s="7">
         <v>597</v>
@@ -16651,9 +16798,15 @@
       <c t="s" r="N120" s="4">
         <v>52</v>
       </c>
-      <c r="O120" s="5"/>
-      <c r="P120" s="5"/>
-      <c r="Q120" s="6"/>
+      <c r="O120" s="5">
+        <v>16036.83</v>
+      </c>
+      <c r="P120" s="5">
+        <v>16036.83</v>
+      </c>
+      <c r="Q120" s="6">
+        <v>-0.16035165392110562</v>
+      </c>
       <c r="R120" s="7"/>
       <c r="S120" s="6"/>
       <c r="T120" s="6"/>
@@ -16671,7 +16824,7 @@
       <c r="AF120" s="9"/>
       <c r="AG120" s="5"/>
       <c r="AH120" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI120" s="11"/>
       <c r="AJ120" s="13"/>
@@ -16743,13 +16896,13 @@
         <v>52</v>
       </c>
       <c r="O121" s="5">
-        <v>60870.619999999995</v>
+        <v>53891.870000000003</v>
       </c>
       <c r="P121" s="5">
-        <v>60870.619999999995</v>
+        <v>53891.870000000003</v>
       </c>
       <c r="Q121" s="6">
-        <v>0.17177008053118148</v>
+        <v>0.037427922532676128</v>
       </c>
       <c r="R121" s="7">
         <v>608</v>
@@ -16872,13 +17025,13 @@
         <v>52</v>
       </c>
       <c r="O122" s="5">
-        <v>52666.040000000001</v>
+        <v>50180.190000000002</v>
       </c>
       <c r="P122" s="5">
-        <v>52666.040000000001</v>
+        <v>50180.190000000002</v>
       </c>
       <c r="Q122" s="6">
-        <v>0.61560595760763137</v>
+        <v>0.5393489603145194</v>
       </c>
       <c r="R122" s="7">
         <v>633</v>
@@ -17003,13 +17156,13 @@
         <v>52</v>
       </c>
       <c r="O123" s="5">
-        <v>62900.319999999992</v>
+        <v>54512.970000000001</v>
       </c>
       <c r="P123" s="5">
-        <v>62900.319999999992</v>
+        <v>54512.970000000008</v>
       </c>
       <c r="Q123" s="6">
-        <v>0.33878635909217536</v>
+        <v>0.16026787510144613</v>
       </c>
       <c r="R123" s="7">
         <v>751</v>
@@ -17134,13 +17287,13 @@
         <v>52</v>
       </c>
       <c r="O124" s="5">
-        <v>23451.670000000002</v>
+        <v>21908.52</v>
       </c>
       <c r="P124" s="5">
-        <v>23451.670000000002</v>
+        <v>21908.52</v>
       </c>
       <c r="Q124" s="6">
-        <v>0.39336744909520749</v>
+        <v>0.30168208173879885</v>
       </c>
       <c r="R124" s="7">
         <v>277</v>
@@ -17265,13 +17418,13 @@
         <v>52</v>
       </c>
       <c r="O125" s="5">
-        <v>34145.580000000002</v>
+        <v>32397.23</v>
       </c>
       <c r="P125" s="5">
-        <v>34145.580000000002</v>
+        <v>32397.23</v>
       </c>
       <c r="Q125" s="6">
-        <v>0.3336028223704024</v>
+        <v>0.26531859657920775</v>
       </c>
       <c r="R125" s="7">
         <v>409</v>
@@ -17396,13 +17549,13 @@
         <v>52</v>
       </c>
       <c r="O126" s="5">
-        <v>30182.740000000002</v>
+        <v>28549.849999999999</v>
       </c>
       <c r="P126" s="5">
-        <v>30182.740000000002</v>
+        <v>28549.849999999999</v>
       </c>
       <c r="Q126" s="6">
-        <v>0.14686870191416235</v>
+        <v>0.084822962042016004</v>
       </c>
       <c r="R126" s="7">
         <v>350</v>
@@ -17529,13 +17682,13 @@
         <v>52</v>
       </c>
       <c r="O127" s="5">
-        <v>53537.510000000002</v>
+        <v>47748.199999999997</v>
       </c>
       <c r="P127" s="5">
-        <v>53537.510000000002</v>
+        <v>47748.199999999997</v>
       </c>
       <c r="Q127" s="6">
-        <v>0.082998041450370597</v>
+        <v>-0.034112586058250072</v>
       </c>
       <c r="R127" s="7">
         <v>551</v>
@@ -17660,13 +17813,13 @@
         <v>52</v>
       </c>
       <c r="O128" s="5">
-        <v>31426.219999999998</v>
+        <v>29641.119999999999</v>
       </c>
       <c r="P128" s="5">
-        <v>31426.219999999998</v>
+        <v>29641.119999999999</v>
       </c>
       <c r="Q128" s="6">
-        <v>0.11058486765381481</v>
+        <v>0.047500441742940991</v>
       </c>
       <c r="R128" s="7">
         <v>371</v>
@@ -17787,13 +17940,13 @@
         <v>52</v>
       </c>
       <c r="O129" s="5">
-        <v>27685.880000000001</v>
+        <v>26188.07</v>
       </c>
       <c r="P129" s="5">
-        <v>27685.880000000001</v>
+        <v>26188.07</v>
       </c>
       <c r="Q129" s="6">
-        <v>0.17861857607307918</v>
+        <v>0.11485514542077491</v>
       </c>
       <c r="R129" s="7">
         <v>304</v>
@@ -17920,13 +18073,13 @@
         <v>52</v>
       </c>
       <c r="O130" s="5">
-        <v>31820.730000000003</v>
+        <v>30099.220000000001</v>
       </c>
       <c r="P130" s="5">
-        <v>31820.730000000003</v>
+        <v>30099.220000000001</v>
       </c>
       <c r="Q130" s="6">
-        <v>0.12822504701420789</v>
+        <v>0.067187770349422582</v>
       </c>
       <c r="R130" s="7">
         <v>327</v>
@@ -18053,13 +18206,13 @@
         <v>52</v>
       </c>
       <c r="O131" s="5">
-        <v>24897.560000000001</v>
+        <v>23206.919999999998</v>
       </c>
       <c r="P131" s="5">
-        <v>24897.560000000001</v>
+        <v>23206.920000000002</v>
       </c>
       <c r="Q131" s="6">
-        <v>0.11577051952946604</v>
+        <v>0.040005413585859628</v>
       </c>
       <c r="R131" s="7">
         <v>278</v>
@@ -18184,13 +18337,13 @@
         <v>52</v>
       </c>
       <c r="O132" s="5">
-        <v>24141.870000000003</v>
+        <v>22835.790000000001</v>
       </c>
       <c r="P132" s="5">
-        <v>24141.870000000003</v>
+        <v>22835.790000000001</v>
       </c>
       <c r="Q132" s="6">
-        <v>-0.11847037610721245</v>
+        <v>-0.16616130523465344</v>
       </c>
       <c r="R132" s="7">
         <v>264</v>
@@ -18315,13 +18468,13 @@
         <v>52</v>
       </c>
       <c r="O133" s="5">
-        <v>72993.479999999996</v>
+        <v>64241.830000000002</v>
       </c>
       <c r="P133" s="5">
-        <v>72993.479999999996</v>
+        <v>64241.830000000002</v>
       </c>
       <c r="Q133" s="6">
-        <v>0.085509987658284548</v>
+        <v>-0.044638670598447505</v>
       </c>
       <c r="R133" s="7">
         <v>722</v>
@@ -18445,9 +18598,15 @@
       <c t="s" r="N134" s="4">
         <v>52</v>
       </c>
-      <c r="O134" s="5"/>
-      <c r="P134" s="5"/>
-      <c r="Q134" s="6"/>
+      <c r="O134" s="5">
+        <v>27407.279999999999</v>
+      </c>
+      <c r="P134" s="5">
+        <v>27407.279999999999</v>
+      </c>
+      <c r="Q134" s="6">
+        <v>-0.055154332638677084</v>
+      </c>
       <c r="R134" s="7"/>
       <c r="S134" s="6"/>
       <c r="T134" s="6"/>
@@ -18541,13 +18700,13 @@
         <v>52</v>
       </c>
       <c r="O135" s="5">
-        <v>32418.170000000002</v>
+        <v>30664.34</v>
       </c>
       <c r="P135" s="5">
-        <v>32418.170000000002</v>
+        <v>30664.34</v>
       </c>
       <c r="Q135" s="6">
-        <v>0.082438596022598398</v>
+        <v>0.023878434148491445</v>
       </c>
       <c r="R135" s="7">
         <v>337</v>
@@ -18672,13 +18831,13 @@
         <v>52</v>
       </c>
       <c r="O136" s="5">
-        <v>30311</v>
+        <v>28671.169999999998</v>
       </c>
       <c r="P136" s="5">
-        <v>30311</v>
+        <v>28671.170000000002</v>
       </c>
       <c r="Q136" s="6">
-        <v>0.23739125216515911</v>
+        <v>0.17044818538946749</v>
       </c>
       <c r="R136" s="7">
         <v>320</v>
@@ -18803,13 +18962,13 @@
         <v>52</v>
       </c>
       <c r="O137" s="5">
-        <v>32742.850000000002</v>
+        <v>30971.459999999999</v>
       </c>
       <c r="P137" s="5">
-        <v>32742.850000000002</v>
+        <v>30971.459999999999</v>
       </c>
       <c r="Q137" s="6">
-        <v>-0.15889577817331879</v>
+        <v>-0.20439956319818875</v>
       </c>
       <c r="R137" s="7">
         <v>314</v>
@@ -18934,13 +19093,13 @@
         <v>52</v>
       </c>
       <c r="O138" s="5">
-        <v>56749.770000000004</v>
+        <v>53510.57</v>
       </c>
       <c r="P138" s="5">
-        <v>56749.770000000004</v>
+        <v>53510.57</v>
       </c>
       <c r="Q138" s="6">
-        <v>0.092207935678218611</v>
+        <v>0.029866186183042043</v>
       </c>
       <c r="R138" s="7">
         <v>616</v>
@@ -19061,13 +19220,13 @@
         <v>52</v>
       </c>
       <c r="O139" s="5">
-        <v>31261.119999999999</v>
+        <v>29569.880000000001</v>
       </c>
       <c r="P139" s="5">
-        <v>31261.119999999999</v>
+        <v>29569.880000000001</v>
       </c>
       <c r="Q139" s="6">
-        <v>-0.072681267112214787</v>
+        <v>-0.12284960829158176</v>
       </c>
       <c r="R139" s="7">
         <v>310</v>
@@ -19190,13 +19349,13 @@
         <v>52</v>
       </c>
       <c r="O140" s="5">
-        <v>35692.550000000003</v>
+        <v>32380.110000000001</v>
       </c>
       <c r="P140" s="5">
-        <v>35692.550000000003</v>
+        <v>32380.110000000004</v>
       </c>
       <c r="Q140" s="6">
-        <v>0.14667749116279682</v>
+        <v>0.04026031478208747</v>
       </c>
       <c r="R140" s="7">
         <v>450.00000000000006</v>
@@ -19321,13 +19480,13 @@
         <v>52</v>
       </c>
       <c r="O141" s="5">
-        <v>37978.809999999998</v>
+        <v>35609.559999999998</v>
       </c>
       <c r="P141" s="5">
-        <v>37978.809999999998</v>
+        <v>35609.559999999998</v>
       </c>
       <c r="Q141" s="6">
-        <v>0.039539883807659715</v>
+        <v>-0.025310222599341792</v>
       </c>
       <c r="R141" s="7">
         <v>417</v>
@@ -19452,13 +19611,13 @@
         <v>52</v>
       </c>
       <c r="O142" s="5">
-        <v>83859.470000000001</v>
+        <v>75830.660000000003</v>
       </c>
       <c r="P142" s="5">
-        <v>83859.470000000001</v>
+        <v>75830.660000000003</v>
       </c>
       <c r="Q142" s="6">
-        <v>0.21424843975473951</v>
+        <v>0.097994783303211097</v>
       </c>
       <c r="R142" s="7">
         <v>859</v>
@@ -19541,7 +19700,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="143" ht="24.75" customHeight="1">
+    <row r="143" ht="13.5" customHeight="1">
       <c r="A143" s="2">
         <v>19876</v>
       </c>
@@ -19583,13 +19742,13 @@
         <v>52</v>
       </c>
       <c r="O143" s="5">
-        <v>45669.399999999994</v>
+        <v>43422.459999999999</v>
       </c>
       <c r="P143" s="5">
-        <v>45669.399999999987</v>
+        <v>43422.459999999999</v>
       </c>
       <c r="Q143" s="6">
-        <v>-0.041641004118249003</v>
+        <v>-0.088792382551215798</v>
       </c>
       <c r="R143" s="7">
         <v>511</v>
@@ -19714,13 +19873,13 @@
         <v>52</v>
       </c>
       <c r="O144" s="5">
-        <v>34431.659999999996</v>
+        <v>31883.810000000001</v>
       </c>
       <c r="P144" s="5">
-        <v>34431.659999999996</v>
+        <v>31883.810000000001</v>
       </c>
       <c r="Q144" s="6">
-        <v>0.25808866704204081</v>
+        <v>0.16499349793537976</v>
       </c>
       <c r="R144" s="7">
         <v>346</v>
@@ -19845,13 +20004,13 @@
         <v>52</v>
       </c>
       <c r="O145" s="5">
-        <v>38297.080000000002</v>
+        <v>34690.910000000003</v>
       </c>
       <c r="P145" s="5">
-        <v>38297.080000000002</v>
+        <v>34690.910000000003</v>
       </c>
       <c r="Q145" s="6">
-        <v>0.28949870703587988</v>
+        <v>0.16807557105915327</v>
       </c>
       <c r="R145" s="7">
         <v>334</v>
@@ -19976,13 +20135,13 @@
         <v>52</v>
       </c>
       <c r="O146" s="5">
-        <v>80362.87000000001</v>
+        <v>67716.100000000006</v>
       </c>
       <c r="P146" s="5">
-        <v>80362.87000000001</v>
+        <v>67716.100000000006</v>
       </c>
       <c r="Q146" s="6">
-        <v>0.030592605492826719</v>
+        <v>-0.13159258830834686</v>
       </c>
       <c r="R146" s="7">
         <v>704</v>
@@ -20107,13 +20266,13 @@
         <v>52</v>
       </c>
       <c r="O147" s="5">
-        <v>44767.420000000006</v>
+        <v>40509.059999999998</v>
       </c>
       <c r="P147" s="5">
-        <v>44767.420000000006</v>
+        <v>40509.059999999998</v>
       </c>
       <c r="Q147" s="6">
-        <v>0.30294505253991444</v>
+        <v>0.17900650316776234</v>
       </c>
       <c r="R147" s="7">
         <v>458</v>
@@ -20238,13 +20397,13 @@
         <v>52</v>
       </c>
       <c r="O148" s="5">
-        <v>28649</v>
+        <v>26822.029999999999</v>
       </c>
       <c r="P148" s="5">
-        <v>28649</v>
+        <v>26822.029999999999</v>
       </c>
       <c r="Q148" s="6">
-        <v>-0.21516426788022303</v>
+        <v>-0.2652138799962086</v>
       </c>
       <c r="R148" s="7">
         <v>314</v>
@@ -20369,13 +20528,13 @@
         <v>52</v>
       </c>
       <c r="O149" s="5">
-        <v>27130.09</v>
+        <v>24669.610000000001</v>
       </c>
       <c r="P149" s="5">
-        <v>27130.09</v>
+        <v>24669.610000000004</v>
       </c>
       <c r="Q149" s="6">
-        <v>0.07803338435398488</v>
+        <v>-0.019735535009544392</v>
       </c>
       <c r="R149" s="7">
         <v>301</v>
@@ -20500,13 +20659,13 @@
         <v>52</v>
       </c>
       <c r="O150" s="5">
-        <v>33106.799999999996</v>
+        <v>31315.720000000001</v>
       </c>
       <c r="P150" s="5">
-        <v>33106.799999999996</v>
+        <v>31315.720000000001</v>
       </c>
       <c r="Q150" s="6">
-        <v>-0.024470449293785279</v>
+        <v>-0.077246660455204674</v>
       </c>
       <c r="R150" s="7">
         <v>349</v>
@@ -20631,13 +20790,13 @@
         <v>52</v>
       </c>
       <c r="O151" s="5">
-        <v>25352.420000000002</v>
+        <v>23862.709999999999</v>
       </c>
       <c r="P151" s="5">
-        <v>25352.420000000002</v>
+        <v>23862.709999999999</v>
       </c>
       <c r="Q151" s="6">
-        <v>0.72052165851956995</v>
+        <v>0.61942368365511147</v>
       </c>
       <c r="R151" s="7">
         <v>274</v>
@@ -20762,13 +20921,13 @@
         <v>52</v>
       </c>
       <c r="O152" s="5">
-        <v>29636.189999999999</v>
+        <v>27910.880000000001</v>
       </c>
       <c r="P152" s="5">
-        <v>29636.189999999999</v>
+        <v>27910.880000000001</v>
       </c>
       <c r="Q152" s="6">
-        <v>0.065267526514696694</v>
+        <v>0.0032515684522376187</v>
       </c>
       <c r="R152" s="7">
         <v>291</v>
@@ -20893,13 +21052,13 @@
         <v>52</v>
       </c>
       <c r="O153" s="5">
-        <v>26272.07</v>
+        <v>28599.84</v>
       </c>
       <c r="P153" s="5">
-        <v>26272.07</v>
+        <v>28599.84</v>
       </c>
       <c r="Q153" s="6">
-        <v>-0.031645056397531679</v>
+        <v>0.054153572605417866</v>
       </c>
       <c r="R153" s="7">
         <v>428</v>
@@ -21022,13 +21181,13 @@
         <v>52</v>
       </c>
       <c r="O154" s="5">
-        <v>15389.32</v>
+        <v>14052.690000000001</v>
       </c>
       <c r="P154" s="5">
-        <v>15389.319999999998</v>
+        <v>14052.690000000001</v>
       </c>
       <c r="Q154" s="6">
-        <v>-0.40921987857569253</v>
+        <v>-0.46053172560333056</v>
       </c>
       <c r="R154" s="7">
         <v>184</v>
@@ -21153,13 +21312,13 @@
         <v>52</v>
       </c>
       <c r="O155" s="5">
-        <v>21632.93</v>
+        <v>19773.330000000002</v>
       </c>
       <c r="P155" s="5">
-        <v>21632.93</v>
+        <v>19773.329999999998</v>
       </c>
       <c r="Q155" s="6">
-        <v>0.22966775614608492</v>
+        <v>0.12396362086116253</v>
       </c>
       <c r="R155" s="7">
         <v>291</v>
@@ -21284,13 +21443,13 @@
         <v>52</v>
       </c>
       <c r="O156" s="5">
-        <v>34349.529999999999</v>
+        <v>32525.52</v>
       </c>
       <c r="P156" s="5">
-        <v>34349.529999999999</v>
+        <v>32525.52</v>
       </c>
       <c r="Q156" s="6">
-        <v>0.35328460654139837</v>
+        <v>0.28142322575459944</v>
       </c>
       <c r="R156" s="7">
         <v>428</v>
@@ -21413,13 +21572,13 @@
         <v>52</v>
       </c>
       <c r="O157" s="5">
-        <v>50119.059999999998</v>
+        <v>47402.589999999997</v>
       </c>
       <c r="P157" s="5">
-        <v>50119.059999999998</v>
+        <v>47402.590000000004</v>
       </c>
       <c r="Q157" s="6">
-        <v>1.0894877865647414</v>
+        <v>0.97623684196263749</v>
       </c>
       <c r="R157" s="7">
         <v>587</v>
@@ -21542,13 +21701,13 @@
         <v>52</v>
       </c>
       <c r="O158" s="5">
-        <v>7003.1000000000004</v>
+        <v>12802.16</v>
       </c>
       <c r="P158" s="5">
-        <v>12255.425000000001</v>
+        <v>12802.16</v>
       </c>
       <c r="Q158" s="6">
-        <v>-0.40621646305273118</v>
+        <v>-0.37972678667897319</v>
       </c>
       <c r="R158" s="7">
         <v>136.5</v>
@@ -21673,13 +21832,13 @@
         <v>52</v>
       </c>
       <c r="O159" s="5">
-        <v>18156.240000000002</v>
+        <v>16368.49</v>
       </c>
       <c r="P159" s="5">
-        <v>18156.240000000002</v>
+        <v>16368.49</v>
       </c>
       <c r="Q159" s="6">
-        <v>-0.24061922425904259</v>
+        <v>-0.31539147786611632</v>
       </c>
       <c r="R159" s="7">
         <v>219</v>
@@ -21688,10 +21847,10 @@
         <v>-0.30914826498422709</v>
       </c>
       <c r="T159" s="6">
-        <v>0.60313706472265183</v>
+        <v>0.31164309350394132</v>
       </c>
       <c r="U159" s="6">
-        <v>0.28979906081875978</v>
+        <v>-0.0016949103999506503</v>
       </c>
       <c r="V159" s="6">
         <v>0.053501523443179856</v>
@@ -21804,13 +21963,13 @@
         <v>52</v>
       </c>
       <c r="O160" s="5">
-        <v>30578.43</v>
+        <v>27855.490000000002</v>
       </c>
       <c r="P160" s="5">
-        <v>30578.43</v>
+        <v>27855.490000000002</v>
       </c>
       <c r="Q160" s="6">
-        <v>0.34970080390329872</v>
+        <v>0.22951300135815655</v>
       </c>
       <c r="R160" s="7">
         <v>347</v>
@@ -21935,13 +22094,13 @@
         <v>52</v>
       </c>
       <c r="O161" s="5">
-        <v>35929.57</v>
+        <v>32554.939999999999</v>
       </c>
       <c r="P161" s="5">
-        <v>35929.57</v>
+        <v>32554.939999999999</v>
       </c>
       <c r="Q161" s="6">
-        <v>0.30300270830522757</v>
+        <v>0.18062016853288765</v>
       </c>
       <c r="R161" s="7">
         <v>466</v>
@@ -22066,13 +22225,13 @@
         <v>52</v>
       </c>
       <c r="O162" s="5">
-        <v>35337.599999999999</v>
+        <v>32126.400000000001</v>
       </c>
       <c r="P162" s="5">
-        <v>35337.599999999999</v>
+        <v>32126.400000000001</v>
       </c>
       <c r="Q162" s="6">
-        <v>1.1246689373829444</v>
+        <v>0.93159592473567621</v>
       </c>
       <c r="R162" s="7">
         <v>406</v>
@@ -22121,7 +22280,7 @@
         <v>-744.39999999999998</v>
       </c>
       <c r="AH162" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AI162" s="11"/>
       <c r="AJ162" s="12">
@@ -22197,13 +22356,13 @@
         <v>52</v>
       </c>
       <c r="O163" s="5">
-        <v>52073.669999999998</v>
+        <v>46604.660000000003</v>
       </c>
       <c r="P163" s="5">
-        <v>52073.669999999998</v>
+        <v>46604.659999999996</v>
       </c>
       <c r="Q163" s="6">
-        <v>0.20957365707763254</v>
+        <v>0.082538815356391515</v>
       </c>
       <c r="R163" s="7">
         <v>569</v>
@@ -22327,9 +22486,15 @@
       <c t="s" r="N164" s="4">
         <v>52</v>
       </c>
-      <c r="O164" s="5"/>
-      <c r="P164" s="5"/>
-      <c r="Q164" s="6"/>
+      <c r="O164" s="5">
+        <v>33575.550000000003</v>
+      </c>
+      <c r="P164" s="5">
+        <v>33575.550000000003</v>
+      </c>
+      <c r="Q164" s="6">
+        <v>0.26196260818121764</v>
+      </c>
       <c r="R164" s="7"/>
       <c r="S164" s="6"/>
       <c r="T164" s="6"/>
@@ -22421,13 +22586,13 @@
         <v>52</v>
       </c>
       <c r="O165" s="5">
-        <v>16881.859999999997</v>
+        <v>15456.780000000001</v>
       </c>
       <c r="P165" s="5">
-        <v>16881.859999999997</v>
+        <v>15456.780000000001</v>
       </c>
       <c r="Q165" s="6">
-        <v>-0.050463860294076568</v>
+        <v>-0.13061882911694989</v>
       </c>
       <c r="R165" s="7">
         <v>228</v>
@@ -22552,13 +22717,13 @@
         <v>52</v>
       </c>
       <c r="O166" s="5">
-        <v>12048.09</v>
+        <v>11153.370000000001</v>
       </c>
       <c r="P166" s="5">
-        <v>12048.09</v>
+        <v>11153.370000000001</v>
       </c>
       <c r="Q166" s="6">
-        <v>-0.16308763340622445</v>
+        <v>-0.22523874886425821</v>
       </c>
       <c r="R166" s="7">
         <v>160</v>
@@ -22685,13 +22850,13 @@
         <v>52</v>
       </c>
       <c r="O167" s="5">
-        <v>27814.060000000001</v>
+        <v>25223.82</v>
       </c>
       <c r="P167" s="5">
-        <v>27814.060000000001</v>
+        <v>25223.82</v>
       </c>
       <c r="Q167" s="6">
-        <v>0.058678219457347858</v>
+        <v>-0.039913308394652347</v>
       </c>
       <c r="R167" s="7">
         <v>317</v>
@@ -22816,13 +22981,13 @@
         <v>52</v>
       </c>
       <c r="O168" s="5">
-        <v>34377.979999999996</v>
+        <v>31162.57</v>
       </c>
       <c r="P168" s="5">
-        <v>34377.979999999996</v>
+        <v>31162.57</v>
       </c>
       <c r="Q168" s="6">
-        <v>0.34639784125044537</v>
+        <v>0.22046778128953171</v>
       </c>
       <c r="R168" s="7">
         <v>422</v>
@@ -22947,13 +23112,13 @@
         <v>52</v>
       </c>
       <c r="O169" s="5">
-        <v>34695.910000000003</v>
+        <v>30689.380000000001</v>
       </c>
       <c r="P169" s="5">
-        <v>34695.910000000003</v>
+        <v>30689.380000000001</v>
       </c>
       <c r="Q169" s="6">
-        <v>0.0235500309461254</v>
+        <v>-0.094644992775303916</v>
       </c>
       <c r="R169" s="7">
         <v>388</v>
@@ -23078,13 +23243,13 @@
         <v>52</v>
       </c>
       <c r="O170" s="5">
-        <v>22184.240000000002</v>
+        <v>20230.049999999999</v>
       </c>
       <c r="P170" s="5">
-        <v>22184.240000000002</v>
+        <v>20230.049999999999</v>
       </c>
       <c r="Q170" s="6">
-        <v>0.77690702657241872</v>
+        <v>0.62038086465487896</v>
       </c>
       <c r="R170" s="7">
         <v>263</v>
@@ -23209,13 +23374,13 @@
         <v>52</v>
       </c>
       <c r="O171" s="5">
-        <v>18442.689999999999</v>
+        <v>16804.310000000001</v>
       </c>
       <c r="P171" s="5">
-        <v>18442.689999999999</v>
+        <v>16804.310000000001</v>
       </c>
       <c r="Q171" s="6">
-        <v>-0.25955363699250789</v>
+        <v>-0.32533213851393517</v>
       </c>
       <c r="R171" s="7">
         <v>201</v>
@@ -23338,13 +23503,13 @@
         <v>52</v>
       </c>
       <c r="O172" s="5">
-        <v>45405.619999999995</v>
+        <v>40938.93</v>
       </c>
       <c r="P172" s="5">
-        <v>45405.619999999995</v>
+        <v>40938.93</v>
       </c>
       <c r="Q172" s="6">
-        <v>0.45351333753540879</v>
+        <v>0.31052677574777032</v>
       </c>
       <c r="R172" s="7">
         <v>518</v>
@@ -23471,13 +23636,13 @@
         <v>52</v>
       </c>
       <c r="O173" s="5">
-        <v>18915.139999999999</v>
+        <v>17329.75</v>
       </c>
       <c r="P173" s="5">
-        <v>18915.139999999996</v>
+        <v>17329.75</v>
       </c>
       <c r="Q173" s="6">
-        <v>0.090576257036226071</v>
+        <v>-0.00083140328998143609</v>
       </c>
       <c r="R173" s="7">
         <v>236.99999999999997</v>
@@ -23526,7 +23691,7 @@
         <v>-1589.7</v>
       </c>
       <c r="AH173" s="10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI173" s="11"/>
       <c r="AJ173" s="12">
@@ -23602,13 +23767,13 @@
         <v>52</v>
       </c>
       <c r="O174" s="5">
-        <v>45619.729999999996</v>
+        <v>41003.480000000003</v>
       </c>
       <c r="P174" s="5">
-        <v>45619.729999999996</v>
+        <v>41003.480000000003</v>
       </c>
       <c r="Q174" s="6">
-        <v>0.13356968972756644</v>
+        <v>0.018864033201215546</v>
       </c>
       <c r="R174" s="7">
         <v>517</v>
@@ -23685,7 +23850,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR174" s="4">
-        <v>226</v>
+        <v>267</v>
       </c>
       <c t="s" r="AS174" s="4">
         <v>56</v>
@@ -23702,10 +23867,10 @@
         <v>44</v>
       </c>
       <c t="s" r="D175" s="4">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c t="s" r="E175" s="4">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="F175" s="4">
         <v>47</v>
@@ -23733,10 +23898,10 @@
         <v>52</v>
       </c>
       <c r="O175" s="5">
-        <v>33944.580000000002</v>
+        <v>31032.07</v>
       </c>
       <c r="P175" s="5">
-        <v>33944.580000000002</v>
+        <v>31032.07</v>
       </c>
       <c r="Q175" s="6"/>
       <c r="R175" s="7">
@@ -23812,7 +23977,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR175" s="4">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="AS175" s="4">
         <v>56</v>
@@ -23860,13 +24025,13 @@
         <v>52</v>
       </c>
       <c r="O176" s="5">
-        <v>67634.199999999997</v>
+        <v>60439.050000000003</v>
       </c>
       <c r="P176" s="5">
-        <v>67634.199999999997</v>
+        <v>60439.050000000003</v>
       </c>
       <c r="Q176" s="6">
-        <v>0.17220214560505198</v>
+        <v>0.047499402496533172</v>
       </c>
       <c r="R176" s="7">
         <v>686</v>
@@ -23943,7 +24108,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR176" s="4">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="AS176" s="4">
         <v>56</v>
@@ -23963,7 +24128,7 @@
         <v>89</v>
       </c>
       <c t="s" r="E177" s="4">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c t="s" r="F177" s="4">
         <v>47</v>
@@ -23991,13 +24156,13 @@
         <v>52</v>
       </c>
       <c r="O177" s="5">
-        <v>17631.049999999999</v>
+        <v>16191.299999999999</v>
       </c>
       <c r="P177" s="5">
-        <v>17631.049999999999</v>
+        <v>16191.299999999999</v>
       </c>
       <c r="Q177" s="6">
-        <v>0.14748576955067838</v>
+        <v>0.053782182032601433</v>
       </c>
       <c r="R177" s="7">
         <v>254</v>
@@ -24074,7 +24239,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR177" s="4">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c t="s" r="AS177" s="4">
         <v>56</v>
@@ -24094,7 +24259,7 @@
         <v>80</v>
       </c>
       <c t="s" r="E178" s="4">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c t="s" r="F178" s="4">
         <v>47</v>
@@ -24122,13 +24287,13 @@
         <v>52</v>
       </c>
       <c r="O178" s="5">
-        <v>33712.100000000006</v>
+        <v>29550.200000000001</v>
       </c>
       <c r="P178" s="5">
-        <v>33712.100000000006</v>
+        <v>29550.200000000001</v>
       </c>
       <c r="Q178" s="6">
-        <v>-0.080339143030954241</v>
+        <v>-0.19387512923826489</v>
       </c>
       <c r="R178" s="7">
         <v>364</v>
@@ -24205,7 +24370,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR178" s="4">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="AS178" s="4">
         <v>56</v>
@@ -24225,7 +24390,7 @@
         <v>83</v>
       </c>
       <c t="s" r="E179" s="4">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="F179" s="4">
         <v>47</v>
@@ -24253,13 +24418,13 @@
         <v>52</v>
       </c>
       <c r="O179" s="5">
-        <v>15001.980000000001</v>
+        <v>13848.620000000001</v>
       </c>
       <c r="P179" s="5">
-        <v>15001.980000000001</v>
+        <v>13848.620000000001</v>
       </c>
       <c r="Q179" s="6">
-        <v>-0.034416574948347933</v>
+        <v>-0.10865112926168352</v>
       </c>
       <c r="R179" s="7">
         <v>193</v>
@@ -24336,7 +24501,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR179" s="4">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c t="s" r="AS179" s="4">
         <v>56</v>
@@ -24356,7 +24521,7 @@
         <v>68</v>
       </c>
       <c t="s" r="E180" s="4">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c t="s" r="F180" s="4">
         <v>47</v>
@@ -24384,13 +24549,13 @@
         <v>52</v>
       </c>
       <c r="O180" s="5">
-        <v>13295.93</v>
+        <v>12222.68</v>
       </c>
       <c r="P180" s="5">
-        <v>13295.930000000002</v>
+        <v>12222.680000000002</v>
       </c>
       <c r="Q180" s="6">
-        <v>-0.64535627931540807</v>
+        <v>-0.67398318794269008</v>
       </c>
       <c r="R180" s="7">
         <v>170</v>
@@ -24467,7 +24632,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR180" s="4">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="AS180" s="4">
         <v>56</v>
@@ -24487,7 +24652,7 @@
         <v>204</v>
       </c>
       <c t="s" r="E181" s="4">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c t="s" r="F181" s="4">
         <v>47</v>
@@ -24515,10 +24680,10 @@
         <v>52</v>
       </c>
       <c r="O181" s="5">
-        <v>37691.849999999999</v>
+        <v>35535.860000000001</v>
       </c>
       <c r="P181" s="5">
-        <v>37691.849999999999</v>
+        <v>35535.860000000001</v>
       </c>
       <c r="Q181" s="6"/>
       <c r="R181" s="7">
@@ -24594,7 +24759,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR181" s="4">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="AS181" s="4">
         <v>56</v>
@@ -24614,7 +24779,7 @@
         <v>103</v>
       </c>
       <c t="s" r="E182" s="4">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c t="s" r="F182" s="4">
         <v>47</v>
@@ -24642,10 +24807,10 @@
         <v>52</v>
       </c>
       <c r="O182" s="5">
-        <v>18255.450000000001</v>
+        <v>17092.220000000001</v>
       </c>
       <c r="P182" s="5">
-        <v>18255.450000000001</v>
+        <v>17092.220000000001</v>
       </c>
       <c r="Q182" s="6"/>
       <c r="R182" s="7">
@@ -24721,7 +24886,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR182" s="4">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c t="s" r="AS182" s="4">
         <v>56</v>
@@ -24741,7 +24906,7 @@
         <v>80</v>
       </c>
       <c t="s" r="E183" s="4">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="F183" s="4">
         <v>47</v>
@@ -24769,10 +24934,10 @@
         <v>52</v>
       </c>
       <c r="O183" s="5">
-        <v>20894.169999999998</v>
+        <v>19236.220000000001</v>
       </c>
       <c r="P183" s="5">
-        <v>20894.170000000002</v>
+        <v>19236.220000000001</v>
       </c>
       <c r="Q183" s="6"/>
       <c r="R183" s="7">
@@ -24848,7 +25013,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR183" s="4">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="AS183" s="4">
         <v>56</v>
@@ -24868,7 +25033,7 @@
         <v>45</v>
       </c>
       <c t="s" r="E184" s="4">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c t="s" r="F184" s="4">
         <v>47</v>
@@ -24896,10 +25061,10 @@
         <v>52</v>
       </c>
       <c r="O184" s="5">
-        <v>24510.360000000001</v>
+        <v>21823.549999999999</v>
       </c>
       <c r="P184" s="5">
-        <v>24510.360000000004</v>
+        <v>21823.549999999999</v>
       </c>
       <c r="Q184" s="6"/>
       <c r="R184" s="7">
@@ -24995,7 +25160,7 @@
         <v>80</v>
       </c>
       <c t="s" r="E185" s="4">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c t="s" r="F185" s="4">
         <v>47</v>
@@ -25023,10 +25188,10 @@
         <v>52</v>
       </c>
       <c r="O185" s="5">
-        <v>32620.920000000002</v>
+        <v>30223.560000000001</v>
       </c>
       <c r="P185" s="5">
-        <v>32620.920000000002</v>
+        <v>30223.560000000001</v>
       </c>
       <c r="Q185" s="6"/>
       <c r="R185" s="7">
@@ -25100,7 +25265,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR185" s="4">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c t="s" r="AS185" s="4">
         <v>56</v>
@@ -25120,7 +25285,7 @@
         <v>45</v>
       </c>
       <c t="s" r="E186" s="4">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c t="s" r="F186" s="4">
         <v>47</v>
@@ -25147,8 +25312,12 @@
       <c t="s" r="N186" s="4">
         <v>52</v>
       </c>
-      <c r="O186" s="5"/>
-      <c r="P186" s="5"/>
+      <c r="O186" s="5">
+        <v>34573.07</v>
+      </c>
+      <c r="P186" s="5">
+        <v>34573.07</v>
+      </c>
       <c r="Q186" s="6"/>
       <c r="R186" s="7"/>
       <c r="S186" s="6"/>
@@ -25193,7 +25362,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR186" s="4">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c t="s" r="AS186" s="4">
         <v>56</v>
@@ -25213,7 +25382,7 @@
         <v>89</v>
       </c>
       <c t="s" r="E187" s="4">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c t="s" r="F187" s="4">
         <v>47</v>
@@ -25241,10 +25410,10 @@
         <v>52</v>
       </c>
       <c r="O187" s="5">
-        <v>30840.060000000001</v>
+        <v>29171.610000000001</v>
       </c>
       <c r="P187" s="5">
-        <v>30840.060000000001</v>
+        <v>29171.610000000004</v>
       </c>
       <c r="Q187" s="6"/>
       <c r="R187" s="7">
@@ -25340,7 +25509,7 @@
         <v>80</v>
       </c>
       <c t="s" r="E188" s="4">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c t="s" r="F188" s="4">
         <v>47</v>
@@ -25367,8 +25536,12 @@
       <c t="s" r="N188" s="4">
         <v>52</v>
       </c>
-      <c r="O188" s="5"/>
-      <c r="P188" s="5"/>
+      <c r="O188" s="5">
+        <v>19985.549999999999</v>
+      </c>
+      <c r="P188" s="5">
+        <v>19985.549999999999</v>
+      </c>
       <c r="Q188" s="6"/>
       <c r="R188" s="7"/>
       <c r="S188" s="6"/>
@@ -25421,10 +25594,10 @@
     </row>
     <row r="189" ht="24.75" customHeight="1">
       <c t="s" r="A189" s="14">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c t="s" r="B189" s="14">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C189" s="15"/>
       <c r="D189" s="15"/>
@@ -25441,65 +25614,65 @@
         <v>52</v>
       </c>
       <c t="s" r="O189" s="14">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="P189" s="14">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c t="s" r="Q189" s="14">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c t="s" r="R189" s="14">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c t="s" r="S189" s="14">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c t="s" r="T189" s="14">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c t="s" r="U189" s="14">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c t="s" r="V189" s="14">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c t="s" r="W189" s="14">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c t="s" r="X189" s="14">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c t="s" r="Y189" s="14">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c t="s" r="Z189" s="14">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c t="s" r="AA189" s="14">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="AB189" s="14">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c t="s" r="AC189" s="14">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c t="s" r="AD189" s="14">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="AE189" s="14">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AF189" s="14"/>
       <c t="s" r="AG189" s="14">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c t="s" r="AH189" s="14">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c t="s" r="AI189" s="14">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AJ189" s="15"/>
       <c t="s" r="AK189" s="15">
@@ -25509,10 +25682,10 @@
         <v>52</v>
       </c>
       <c t="s" r="AM189" s="14">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="AN189" s="14">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AO189" s="15"/>
       <c r="AP189" s="15"/>
